--- a/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -776,25 +776,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4456100</v>
+        <v>4468800</v>
       </c>
       <c r="E8" s="3">
-        <v>8512900</v>
+        <v>8537200</v>
       </c>
       <c r="F8" s="3">
-        <v>4174000</v>
+        <v>4185900</v>
       </c>
       <c r="G8" s="3">
-        <v>8930600</v>
+        <v>8956200</v>
       </c>
       <c r="H8" s="3">
-        <v>4309600</v>
+        <v>4321900</v>
       </c>
       <c r="I8" s="3">
-        <v>8199300</v>
+        <v>8222800</v>
       </c>
       <c r="J8" s="3">
-        <v>3953700</v>
+        <v>3965000</v>
       </c>
       <c r="K8" s="3">
         <v>8400700</v>
@@ -853,25 +853,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1843400</v>
+        <v>1848700</v>
       </c>
       <c r="E9" s="3">
-        <v>3495900</v>
+        <v>3505900</v>
       </c>
       <c r="F9" s="3">
-        <v>1704500</v>
+        <v>1709400</v>
       </c>
       <c r="G9" s="3">
-        <v>3881000</v>
+        <v>3892100</v>
       </c>
       <c r="H9" s="3">
-        <v>1796800</v>
+        <v>1801900</v>
       </c>
       <c r="I9" s="3">
-        <v>3313600</v>
+        <v>3323100</v>
       </c>
       <c r="J9" s="3">
-        <v>1585200</v>
+        <v>1589700</v>
       </c>
       <c r="K9" s="3">
         <v>3510300</v>
@@ -930,25 +930,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2612700</v>
+        <v>2620100</v>
       </c>
       <c r="E10" s="3">
-        <v>5017000</v>
+        <v>5031400</v>
       </c>
       <c r="F10" s="3">
-        <v>2469500</v>
+        <v>2476500</v>
       </c>
       <c r="G10" s="3">
-        <v>5049600</v>
+        <v>5064000</v>
       </c>
       <c r="H10" s="3">
-        <v>2512900</v>
+        <v>2520000</v>
       </c>
       <c r="I10" s="3">
-        <v>4885800</v>
+        <v>4899700</v>
       </c>
       <c r="J10" s="3">
-        <v>2368600</v>
+        <v>2375300</v>
       </c>
       <c r="K10" s="3">
         <v>4890400</v>
@@ -1190,25 +1190,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>151900</v>
+        <v>152300</v>
       </c>
       <c r="E14" s="3">
-        <v>466600</v>
+        <v>467900</v>
       </c>
       <c r="F14" s="3">
-        <v>455700</v>
+        <v>457000</v>
       </c>
       <c r="G14" s="3">
-        <v>72700</v>
+        <v>72900</v>
       </c>
       <c r="H14" s="3">
-        <v>327700</v>
+        <v>328600</v>
       </c>
       <c r="I14" s="3">
-        <v>316800</v>
+        <v>317700</v>
       </c>
       <c r="J14" s="3">
-        <v>77000</v>
+        <v>77300</v>
       </c>
       <c r="K14" s="3">
         <v>4467600</v>
@@ -1267,25 +1267,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1317200</v>
+        <v>1321000</v>
       </c>
       <c r="E15" s="3">
-        <v>2635500</v>
+        <v>2643000</v>
       </c>
       <c r="F15" s="3">
-        <v>1303100</v>
+        <v>1306800</v>
       </c>
       <c r="G15" s="3">
-        <v>2693000</v>
+        <v>2700700</v>
       </c>
       <c r="H15" s="3">
-        <v>1350800</v>
+        <v>1354700</v>
       </c>
       <c r="I15" s="3">
-        <v>2490100</v>
+        <v>2497200</v>
       </c>
       <c r="J15" s="3">
-        <v>1201100</v>
+        <v>1204500</v>
       </c>
       <c r="K15" s="3">
         <v>2408900</v>
@@ -1370,25 +1370,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4099100</v>
+        <v>4110800</v>
       </c>
       <c r="E17" s="3">
-        <v>8253600</v>
+        <v>8277200</v>
       </c>
       <c r="F17" s="3">
-        <v>4349800</v>
+        <v>4362200</v>
       </c>
       <c r="G17" s="3">
-        <v>8703900</v>
+        <v>8728700</v>
       </c>
       <c r="H17" s="3">
-        <v>4265100</v>
+        <v>4277300</v>
       </c>
       <c r="I17" s="3">
-        <v>7768600</v>
+        <v>7790800</v>
       </c>
       <c r="J17" s="3">
-        <v>3727000</v>
+        <v>3737600</v>
       </c>
       <c r="K17" s="3">
         <v>12769600</v>
@@ -1447,25 +1447,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>357000</v>
+        <v>358000</v>
       </c>
       <c r="E18" s="3">
-        <v>259300</v>
+        <v>260100</v>
       </c>
       <c r="F18" s="3">
-        <v>-175800</v>
+        <v>-176300</v>
       </c>
       <c r="G18" s="3">
-        <v>226800</v>
+        <v>227400</v>
       </c>
       <c r="H18" s="3">
-        <v>44500</v>
+        <v>44600</v>
       </c>
       <c r="I18" s="3">
-        <v>430700</v>
+        <v>432000</v>
       </c>
       <c r="J18" s="3">
-        <v>226800</v>
+        <v>227400</v>
       </c>
       <c r="K18" s="3">
         <v>-4368900</v>
@@ -1553,25 +1553,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-534900</v>
+        <v>-536400</v>
       </c>
       <c r="E20" s="3">
-        <v>-607600</v>
+        <v>-609300</v>
       </c>
       <c r="F20" s="3">
-        <v>-406900</v>
+        <v>-408000</v>
       </c>
       <c r="G20" s="3">
-        <v>167100</v>
+        <v>167600</v>
       </c>
       <c r="H20" s="3">
-        <v>-235400</v>
+        <v>-236100</v>
       </c>
       <c r="I20" s="3">
-        <v>-29300</v>
+        <v>-29400</v>
       </c>
       <c r="J20" s="3">
-        <v>-326600</v>
+        <v>-327500</v>
       </c>
       <c r="K20" s="3">
         <v>173500</v>
@@ -1630,25 +1630,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1139300</v>
+        <v>1142500</v>
       </c>
       <c r="E21" s="3">
-        <v>2287200</v>
+        <v>2293700</v>
       </c>
       <c r="F21" s="3">
-        <v>720400</v>
+        <v>722500</v>
       </c>
       <c r="G21" s="3">
-        <v>3086800</v>
+        <v>3095600</v>
       </c>
       <c r="H21" s="3">
-        <v>1159900</v>
+        <v>1163200</v>
       </c>
       <c r="I21" s="3">
-        <v>2891500</v>
+        <v>2899800</v>
       </c>
       <c r="J21" s="3">
-        <v>1101300</v>
+        <v>1104400</v>
       </c>
       <c r="K21" s="3">
         <v>-1786600</v>
@@ -1710,19 +1710,19 @@
         <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>226800</v>
+        <v>227400</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="3">
-        <v>751900</v>
+        <v>754100</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I22" s="3">
-        <v>681400</v>
+        <v>683300</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>8</v>
@@ -1784,25 +1784,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-177900</v>
+        <v>-178400</v>
       </c>
       <c r="E23" s="3">
-        <v>-575100</v>
+        <v>-576700</v>
       </c>
       <c r="F23" s="3">
-        <v>-582600</v>
+        <v>-584300</v>
       </c>
       <c r="G23" s="3">
-        <v>-358100</v>
+        <v>-359100</v>
       </c>
       <c r="H23" s="3">
-        <v>-191000</v>
+        <v>-191500</v>
       </c>
       <c r="I23" s="3">
-        <v>-279900</v>
+        <v>-280700</v>
       </c>
       <c r="J23" s="3">
-        <v>-99800</v>
+        <v>-100100</v>
       </c>
       <c r="K23" s="3">
         <v>-4843800</v>
@@ -1861,25 +1861,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>68400</v>
+        <v>68600</v>
       </c>
       <c r="E24" s="3">
-        <v>155200</v>
+        <v>155600</v>
       </c>
       <c r="F24" s="3">
-        <v>92200</v>
+        <v>92500</v>
       </c>
       <c r="G24" s="3">
-        <v>2130900</v>
+        <v>2137000</v>
       </c>
       <c r="H24" s="3">
-        <v>2177600</v>
+        <v>2183800</v>
       </c>
       <c r="I24" s="3">
-        <v>110700</v>
+        <v>111000</v>
       </c>
       <c r="J24" s="3">
-        <v>54300</v>
+        <v>54400</v>
       </c>
       <c r="K24" s="3">
         <v>4213900</v>
@@ -2015,25 +2015,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-246300</v>
+        <v>-247000</v>
       </c>
       <c r="E26" s="3">
-        <v>-730200</v>
+        <v>-732300</v>
       </c>
       <c r="F26" s="3">
-        <v>-674900</v>
+        <v>-676800</v>
       </c>
       <c r="G26" s="3">
-        <v>-2489000</v>
+        <v>-2496100</v>
       </c>
       <c r="H26" s="3">
-        <v>-2368600</v>
+        <v>-2375300</v>
       </c>
       <c r="I26" s="3">
-        <v>-390600</v>
+        <v>-391700</v>
       </c>
       <c r="J26" s="3">
-        <v>-154100</v>
+        <v>-154500</v>
       </c>
       <c r="K26" s="3">
         <v>-9057700</v>
@@ -2092,25 +2092,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-337400</v>
+        <v>-338400</v>
       </c>
       <c r="E27" s="3">
-        <v>-882100</v>
+        <v>-884600</v>
       </c>
       <c r="F27" s="3">
-        <v>-747600</v>
+        <v>-749700</v>
       </c>
       <c r="G27" s="3">
-        <v>-2649600</v>
+        <v>-2657100</v>
       </c>
       <c r="H27" s="3">
-        <v>-2435800</v>
+        <v>-2442800</v>
       </c>
       <c r="I27" s="3">
-        <v>-524100</v>
+        <v>-525600</v>
       </c>
       <c r="J27" s="3">
-        <v>-221300</v>
+        <v>-222000</v>
       </c>
       <c r="K27" s="3">
         <v>-9231100</v>
@@ -2477,25 +2477,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>534900</v>
+        <v>536400</v>
       </c>
       <c r="E32" s="3">
-        <v>607600</v>
+        <v>609300</v>
       </c>
       <c r="F32" s="3">
-        <v>406900</v>
+        <v>408000</v>
       </c>
       <c r="G32" s="3">
-        <v>-167100</v>
+        <v>-167600</v>
       </c>
       <c r="H32" s="3">
-        <v>235400</v>
+        <v>236100</v>
       </c>
       <c r="I32" s="3">
-        <v>29300</v>
+        <v>29400</v>
       </c>
       <c r="J32" s="3">
-        <v>326600</v>
+        <v>327500</v>
       </c>
       <c r="K32" s="3">
         <v>-173500</v>
@@ -2554,25 +2554,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-337400</v>
+        <v>-338400</v>
       </c>
       <c r="E33" s="3">
-        <v>-882100</v>
+        <v>-884600</v>
       </c>
       <c r="F33" s="3">
-        <v>-747600</v>
+        <v>-749700</v>
       </c>
       <c r="G33" s="3">
-        <v>-2649600</v>
+        <v>-2657100</v>
       </c>
       <c r="H33" s="3">
-        <v>-2435800</v>
+        <v>-2442800</v>
       </c>
       <c r="I33" s="3">
-        <v>-524100</v>
+        <v>-525600</v>
       </c>
       <c r="J33" s="3">
-        <v>-221300</v>
+        <v>-222000</v>
       </c>
       <c r="K33" s="3">
         <v>-9231100</v>
@@ -2708,25 +2708,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-337400</v>
+        <v>-338400</v>
       </c>
       <c r="E35" s="3">
-        <v>-882100</v>
+        <v>-884600</v>
       </c>
       <c r="F35" s="3">
-        <v>-747600</v>
+        <v>-749700</v>
       </c>
       <c r="G35" s="3">
-        <v>-2649600</v>
+        <v>-2657100</v>
       </c>
       <c r="H35" s="3">
-        <v>-2435800</v>
+        <v>-2442800</v>
       </c>
       <c r="I35" s="3">
-        <v>-524100</v>
+        <v>-525600</v>
       </c>
       <c r="J35" s="3">
-        <v>-221300</v>
+        <v>-222000</v>
       </c>
       <c r="K35" s="3">
         <v>-9231100</v>
@@ -2925,25 +2925,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3570700</v>
+        <v>3580900</v>
       </c>
       <c r="E41" s="3">
-        <v>2587700</v>
+        <v>2595100</v>
       </c>
       <c r="F41" s="3">
-        <v>2886100</v>
+        <v>2894300</v>
       </c>
       <c r="G41" s="3">
-        <v>3857200</v>
+        <v>3868200</v>
       </c>
       <c r="H41" s="3">
-        <v>3818100</v>
+        <v>3829000</v>
       </c>
       <c r="I41" s="3">
-        <v>2594200</v>
+        <v>2601600</v>
       </c>
       <c r="J41" s="3">
-        <v>3550100</v>
+        <v>3560300</v>
       </c>
       <c r="K41" s="3">
         <v>7484600</v>
@@ -3002,25 +3002,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1976900</v>
+        <v>1982500</v>
       </c>
       <c r="E42" s="3">
-        <v>2058200</v>
+        <v>2064100</v>
       </c>
       <c r="F42" s="3">
-        <v>1821700</v>
+        <v>1826900</v>
       </c>
       <c r="G42" s="3">
-        <v>1736000</v>
+        <v>1741000</v>
       </c>
       <c r="H42" s="3">
-        <v>2069100</v>
+        <v>2075000</v>
       </c>
       <c r="I42" s="3">
-        <v>2043100</v>
+        <v>2048900</v>
       </c>
       <c r="J42" s="3">
-        <v>2302400</v>
+        <v>2308900</v>
       </c>
       <c r="K42" s="3">
         <v>2592100</v>
@@ -3079,25 +3079,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5421700</v>
+        <v>5437200</v>
       </c>
       <c r="E43" s="3">
-        <v>3773600</v>
+        <v>3784400</v>
       </c>
       <c r="F43" s="3">
-        <v>5160300</v>
+        <v>5175000</v>
       </c>
       <c r="G43" s="3">
-        <v>3870200</v>
+        <v>3881300</v>
       </c>
       <c r="H43" s="3">
-        <v>5336000</v>
+        <v>5351300</v>
       </c>
       <c r="I43" s="3">
-        <v>3687900</v>
+        <v>3698500</v>
       </c>
       <c r="J43" s="3">
-        <v>4957400</v>
+        <v>4971500</v>
       </c>
       <c r="K43" s="3">
         <v>3694600</v>
@@ -3156,25 +3156,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>394900</v>
+        <v>396100</v>
       </c>
       <c r="E44" s="3">
-        <v>409000</v>
+        <v>410200</v>
       </c>
       <c r="F44" s="3">
-        <v>393900</v>
+        <v>395000</v>
       </c>
       <c r="G44" s="3">
-        <v>349400</v>
+        <v>350400</v>
       </c>
       <c r="H44" s="3">
-        <v>373200</v>
+        <v>374300</v>
       </c>
       <c r="I44" s="3">
-        <v>351500</v>
+        <v>352500</v>
       </c>
       <c r="J44" s="3">
-        <v>335300</v>
+        <v>336200</v>
       </c>
       <c r="K44" s="3">
         <v>305700</v>
@@ -3236,19 +3236,19 @@
         <v>8</v>
       </c>
       <c r="E45" s="3">
-        <v>1547200</v>
+        <v>1551600</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="3">
-        <v>1289000</v>
+        <v>1292700</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I45" s="3">
-        <v>1356300</v>
+        <v>1360100</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
@@ -3310,25 +3310,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>11364300</v>
+        <v>11396800</v>
       </c>
       <c r="E46" s="3">
-        <v>10375900</v>
+        <v>10405500</v>
       </c>
       <c r="F46" s="3">
-        <v>10261900</v>
+        <v>10291200</v>
       </c>
       <c r="G46" s="3">
-        <v>11101700</v>
+        <v>11133400</v>
       </c>
       <c r="H46" s="3">
-        <v>11596500</v>
+        <v>11629600</v>
       </c>
       <c r="I46" s="3">
-        <v>10033000</v>
+        <v>10061700</v>
       </c>
       <c r="J46" s="3">
-        <v>11145100</v>
+        <v>11177000</v>
       </c>
       <c r="K46" s="3">
         <v>15253300</v>
@@ -3387,25 +3387,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4524500</v>
+        <v>4537400</v>
       </c>
       <c r="E47" s="3">
-        <v>1822800</v>
+        <v>1828000</v>
       </c>
       <c r="F47" s="3">
-        <v>5142900</v>
+        <v>5157600</v>
       </c>
       <c r="G47" s="3">
-        <v>1552600</v>
+        <v>1557100</v>
       </c>
       <c r="H47" s="3">
-        <v>5597500</v>
+        <v>5613500</v>
       </c>
       <c r="I47" s="3">
-        <v>1267300</v>
+        <v>1270900</v>
       </c>
       <c r="J47" s="3">
-        <v>8268800</v>
+        <v>8292400</v>
       </c>
       <c r="K47" s="3">
         <v>4296300</v>
@@ -3464,25 +3464,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>21377800</v>
+        <v>21438800</v>
       </c>
       <c r="E48" s="3">
-        <v>21504700</v>
+        <v>21566100</v>
       </c>
       <c r="F48" s="3">
-        <v>21308300</v>
+        <v>21369200</v>
       </c>
       <c r="G48" s="3">
-        <v>21253000</v>
+        <v>21313700</v>
       </c>
       <c r="H48" s="3">
-        <v>21199800</v>
+        <v>21260400</v>
       </c>
       <c r="I48" s="3">
-        <v>21184600</v>
+        <v>21245200</v>
       </c>
       <c r="J48" s="3">
-        <v>20472900</v>
+        <v>20531400</v>
       </c>
       <c r="K48" s="3">
         <v>19685100</v>
@@ -3541,25 +3541,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>28675500</v>
+        <v>28757400</v>
       </c>
       <c r="E49" s="3">
-        <v>28947800</v>
+        <v>29030500</v>
       </c>
       <c r="F49" s="3">
-        <v>28931500</v>
+        <v>29014200</v>
       </c>
       <c r="G49" s="3">
-        <v>29042200</v>
+        <v>29125200</v>
       </c>
       <c r="H49" s="3">
-        <v>29218000</v>
+        <v>29301400</v>
       </c>
       <c r="I49" s="3">
-        <v>29195200</v>
+        <v>29278600</v>
       </c>
       <c r="J49" s="3">
-        <v>28278400</v>
+        <v>28359200</v>
       </c>
       <c r="K49" s="3">
         <v>27877600</v>
@@ -3772,25 +3772,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>858200</v>
+        <v>860700</v>
       </c>
       <c r="E52" s="3">
-        <v>3890800</v>
+        <v>3901900</v>
       </c>
       <c r="F52" s="3">
-        <v>845200</v>
+        <v>847600</v>
       </c>
       <c r="G52" s="3">
-        <v>4349800</v>
+        <v>4362200</v>
       </c>
       <c r="H52" s="3">
-        <v>859300</v>
+        <v>861800</v>
       </c>
       <c r="I52" s="3">
-        <v>10547300</v>
+        <v>10577400</v>
       </c>
       <c r="J52" s="3">
-        <v>3765000</v>
+        <v>3775700</v>
       </c>
       <c r="K52" s="3">
         <v>7893300</v>
@@ -3926,25 +3926,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>66800200</v>
+        <v>66991100</v>
       </c>
       <c r="E54" s="3">
-        <v>66542000</v>
+        <v>66732100</v>
       </c>
       <c r="F54" s="3">
-        <v>66489900</v>
+        <v>66679900</v>
       </c>
       <c r="G54" s="3">
-        <v>67299300</v>
+        <v>67491600</v>
       </c>
       <c r="H54" s="3">
-        <v>68471100</v>
+        <v>68666700</v>
       </c>
       <c r="I54" s="3">
-        <v>72227400</v>
+        <v>72433700</v>
       </c>
       <c r="J54" s="3">
-        <v>71930100</v>
+        <v>72135600</v>
       </c>
       <c r="K54" s="3">
         <v>75005600</v>
@@ -4061,25 +4061,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8565000</v>
+        <v>8589500</v>
       </c>
       <c r="E57" s="3">
-        <v>5221000</v>
+        <v>5235900</v>
       </c>
       <c r="F57" s="3">
-        <v>8700600</v>
+        <v>8725500</v>
       </c>
       <c r="G57" s="3">
-        <v>5745100</v>
+        <v>5761500</v>
       </c>
       <c r="H57" s="3">
-        <v>8236200</v>
+        <v>8259800</v>
       </c>
       <c r="I57" s="3">
-        <v>4957400</v>
+        <v>4971500</v>
       </c>
       <c r="J57" s="3">
-        <v>10475700</v>
+        <v>10505600</v>
       </c>
       <c r="K57" s="3">
         <v>5595000</v>
@@ -4138,25 +4138,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7533200</v>
+        <v>7554700</v>
       </c>
       <c r="E58" s="3">
-        <v>8904600</v>
+        <v>8930000</v>
       </c>
       <c r="F58" s="3">
-        <v>6517600</v>
+        <v>6536200</v>
       </c>
       <c r="G58" s="3">
+        <v>6126000</v>
+      </c>
+      <c r="H58" s="3">
         <v>6108600</v>
       </c>
-      <c r="H58" s="3">
-        <v>6091200</v>
-      </c>
       <c r="I58" s="3">
-        <v>4649200</v>
+        <v>4662500</v>
       </c>
       <c r="J58" s="3">
-        <v>4134900</v>
+        <v>4146700</v>
       </c>
       <c r="K58" s="3">
         <v>7044500</v>
@@ -4215,25 +4215,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="E59" s="3">
-        <v>3822500</v>
+        <v>3833400</v>
       </c>
       <c r="F59" s="3">
-        <v>46700</v>
+        <v>46800</v>
       </c>
       <c r="G59" s="3">
-        <v>3490400</v>
+        <v>3500400</v>
       </c>
       <c r="H59" s="3">
         <v>9800</v>
       </c>
       <c r="I59" s="3">
-        <v>5800400</v>
+        <v>5817000</v>
       </c>
       <c r="J59" s="3">
-        <v>296200</v>
+        <v>297100</v>
       </c>
       <c r="K59" s="3">
         <v>5100700</v>
@@ -4292,25 +4292,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>16124200</v>
+        <v>16170300</v>
       </c>
       <c r="E60" s="3">
-        <v>17948100</v>
+        <v>17999400</v>
       </c>
       <c r="F60" s="3">
-        <v>15264900</v>
+        <v>15308500</v>
       </c>
       <c r="G60" s="3">
-        <v>15344100</v>
+        <v>15387900</v>
       </c>
       <c r="H60" s="3">
-        <v>14337200</v>
+        <v>14378200</v>
       </c>
       <c r="I60" s="3">
-        <v>15407000</v>
+        <v>15451000</v>
       </c>
       <c r="J60" s="3">
-        <v>14906800</v>
+        <v>14949400</v>
       </c>
       <c r="K60" s="3">
         <v>17740200</v>
@@ -4369,25 +4369,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>28174200</v>
+        <v>28254700</v>
       </c>
       <c r="E61" s="3">
-        <v>25208900</v>
+        <v>25280900</v>
       </c>
       <c r="F61" s="3">
-        <v>28059200</v>
+        <v>28139400</v>
       </c>
       <c r="G61" s="3">
-        <v>28274000</v>
+        <v>28354800</v>
       </c>
       <c r="H61" s="3">
-        <v>29844000</v>
+        <v>29929300</v>
       </c>
       <c r="I61" s="3">
-        <v>28176400</v>
+        <v>28256900</v>
       </c>
       <c r="J61" s="3">
-        <v>28838200</v>
+        <v>28920600</v>
       </c>
       <c r="K61" s="3">
         <v>28346000</v>
@@ -4446,25 +4446,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3186600</v>
+        <v>3195700</v>
       </c>
       <c r="E62" s="3">
-        <v>3568600</v>
+        <v>3578800</v>
       </c>
       <c r="F62" s="3">
-        <v>3452500</v>
+        <v>3462300</v>
       </c>
       <c r="G62" s="3">
-        <v>3364600</v>
+        <v>3374200</v>
       </c>
       <c r="H62" s="3">
-        <v>3511100</v>
+        <v>3521100</v>
       </c>
       <c r="I62" s="3">
-        <v>4204400</v>
+        <v>4216400</v>
       </c>
       <c r="J62" s="3">
-        <v>3517600</v>
+        <v>3527600</v>
       </c>
       <c r="K62" s="3">
         <v>5027000</v>
@@ -4754,25 +4754,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>51618900</v>
+        <v>51766400</v>
       </c>
       <c r="E66" s="3">
-        <v>50887600</v>
+        <v>51033000</v>
       </c>
       <c r="F66" s="3">
-        <v>50797500</v>
+        <v>50942700</v>
       </c>
       <c r="G66" s="3">
-        <v>50958100</v>
+        <v>51103700</v>
       </c>
       <c r="H66" s="3">
-        <v>51695900</v>
+        <v>51843600</v>
       </c>
       <c r="I66" s="3">
-        <v>53142200</v>
+        <v>53294000</v>
       </c>
       <c r="J66" s="3">
-        <v>52632300</v>
+        <v>52782600</v>
       </c>
       <c r="K66" s="3">
         <v>56127100</v>
@@ -5168,25 +5168,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4244500</v>
+        <v>4256600</v>
       </c>
       <c r="E72" s="3">
-        <v>4565700</v>
+        <v>4578700</v>
       </c>
       <c r="F72" s="3">
-        <v>3004400</v>
+        <v>3012900</v>
       </c>
       <c r="G72" s="3">
-        <v>3757400</v>
+        <v>3768100</v>
       </c>
       <c r="H72" s="3">
-        <v>3955900</v>
+        <v>3967200</v>
       </c>
       <c r="I72" s="3">
-        <v>6400400</v>
+        <v>6418700</v>
       </c>
       <c r="J72" s="3">
-        <v>6703100</v>
+        <v>6722300</v>
       </c>
       <c r="K72" s="3">
         <v>6912200</v>
@@ -5476,25 +5476,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>15181300</v>
+        <v>15224700</v>
       </c>
       <c r="E76" s="3">
-        <v>15654400</v>
+        <v>15699100</v>
       </c>
       <c r="F76" s="3">
-        <v>15692400</v>
+        <v>15737200</v>
       </c>
       <c r="G76" s="3">
-        <v>16341200</v>
+        <v>16387900</v>
       </c>
       <c r="H76" s="3">
-        <v>16775200</v>
+        <v>16823100</v>
       </c>
       <c r="I76" s="3">
-        <v>19085200</v>
+        <v>19139700</v>
       </c>
       <c r="J76" s="3">
-        <v>19297800</v>
+        <v>19352900</v>
       </c>
       <c r="K76" s="3">
         <v>18878500</v>
@@ -5712,25 +5712,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-337400</v>
+        <v>-338400</v>
       </c>
       <c r="E81" s="3">
-        <v>-882100</v>
+        <v>-884600</v>
       </c>
       <c r="F81" s="3">
-        <v>-747600</v>
+        <v>-749700</v>
       </c>
       <c r="G81" s="3">
-        <v>-2649600</v>
+        <v>-2657100</v>
       </c>
       <c r="H81" s="3">
-        <v>-2435800</v>
+        <v>-2442800</v>
       </c>
       <c r="I81" s="3">
-        <v>-524100</v>
+        <v>-525600</v>
       </c>
       <c r="J81" s="3">
-        <v>-221300</v>
+        <v>-222000</v>
       </c>
       <c r="K81" s="3">
         <v>-9231100</v>
@@ -5818,25 +5818,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1317200</v>
+        <v>1321000</v>
       </c>
       <c r="E83" s="3">
-        <v>2635500</v>
+        <v>2643000</v>
       </c>
       <c r="F83" s="3">
-        <v>1303100</v>
+        <v>1306800</v>
       </c>
       <c r="G83" s="3">
-        <v>2693000</v>
+        <v>2700700</v>
       </c>
       <c r="H83" s="3">
-        <v>1350800</v>
+        <v>1354700</v>
       </c>
       <c r="I83" s="3">
-        <v>2490100</v>
+        <v>2497200</v>
       </c>
       <c r="J83" s="3">
-        <v>1201100</v>
+        <v>1204500</v>
       </c>
       <c r="K83" s="3">
         <v>2408900</v>
@@ -6280,25 +6280,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>870200</v>
+        <v>872700</v>
       </c>
       <c r="E89" s="3">
-        <v>1880300</v>
+        <v>1885700</v>
       </c>
       <c r="F89" s="3">
-        <v>923300</v>
+        <v>926000</v>
       </c>
       <c r="G89" s="3">
-        <v>2606200</v>
+        <v>2613600</v>
       </c>
       <c r="H89" s="3">
-        <v>1098000</v>
+        <v>1101200</v>
       </c>
       <c r="I89" s="3">
-        <v>2704900</v>
+        <v>2712600</v>
       </c>
       <c r="J89" s="3">
-        <v>1166400</v>
+        <v>1169700</v>
       </c>
       <c r="K89" s="3">
         <v>2613800</v>
@@ -6617,25 +6617,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-955900</v>
+        <v>-958600</v>
       </c>
       <c r="E94" s="3">
-        <v>-2331700</v>
+        <v>-2338300</v>
       </c>
       <c r="F94" s="3">
-        <v>-1253200</v>
+        <v>-1256800</v>
       </c>
       <c r="G94" s="3">
-        <v>-2507400</v>
+        <v>-2514600</v>
       </c>
       <c r="H94" s="3">
-        <v>-1664400</v>
+        <v>-1669100</v>
       </c>
       <c r="I94" s="3">
-        <v>-3281000</v>
+        <v>-3290400</v>
       </c>
       <c r="J94" s="3">
-        <v>-820300</v>
+        <v>-822600</v>
       </c>
       <c r="K94" s="3">
         <v>-3139600</v>
@@ -6723,25 +6723,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-84600</v>
+        <v>-84900</v>
       </c>
       <c r="E96" s="3">
-        <v>-93300</v>
+        <v>-93600</v>
       </c>
       <c r="F96" s="3">
-        <v>-41200</v>
+        <v>-41300</v>
       </c>
       <c r="G96" s="3">
-        <v>-33600</v>
+        <v>-33700</v>
       </c>
       <c r="H96" s="3">
         <v>-17400</v>
       </c>
       <c r="I96" s="3">
-        <v>-40100</v>
+        <v>-40300</v>
       </c>
       <c r="J96" s="3">
-        <v>-28200</v>
+        <v>-28300</v>
       </c>
       <c r="K96" s="3">
         <v>-34700</v>
@@ -7031,25 +7031,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1070900</v>
+        <v>1074000</v>
       </c>
       <c r="E100" s="3">
-        <v>-853900</v>
+        <v>-856300</v>
       </c>
       <c r="F100" s="3">
-        <v>-646700</v>
+        <v>-648500</v>
       </c>
       <c r="G100" s="3">
-        <v>1195700</v>
+        <v>1199100</v>
       </c>
       <c r="H100" s="3">
-        <v>1787000</v>
+        <v>1792100</v>
       </c>
       <c r="I100" s="3">
-        <v>-4308500</v>
+        <v>-4320800</v>
       </c>
       <c r="J100" s="3">
-        <v>-4449600</v>
+        <v>-4462300</v>
       </c>
       <c r="K100" s="3">
         <v>2662500</v>
@@ -7111,22 +7111,22 @@
         <v>-5400</v>
       </c>
       <c r="E101" s="3">
-        <v>35800</v>
+        <v>35900</v>
       </c>
       <c r="F101" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="G101" s="3">
-        <v>-22800</v>
+        <v>-22900</v>
       </c>
       <c r="H101" s="3">
-        <v>11900</v>
+        <v>12000</v>
       </c>
       <c r="I101" s="3">
-        <v>-20600</v>
+        <v>-20700</v>
       </c>
       <c r="J101" s="3">
-        <v>156200</v>
+        <v>156700</v>
       </c>
       <c r="K101" s="3">
         <v>-37900</v>
@@ -7185,25 +7185,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>979800</v>
+        <v>982600</v>
       </c>
       <c r="E102" s="3">
-        <v>-1269500</v>
+        <v>-1273100</v>
       </c>
       <c r="F102" s="3">
-        <v>-972200</v>
+        <v>-974900</v>
       </c>
       <c r="G102" s="3">
-        <v>1271600</v>
+        <v>1275300</v>
       </c>
       <c r="H102" s="3">
-        <v>1232600</v>
+        <v>1236100</v>
       </c>
       <c r="I102" s="3">
-        <v>-4905300</v>
+        <v>-4919300</v>
       </c>
       <c r="J102" s="3">
-        <v>-3947200</v>
+        <v>-3958500</v>
       </c>
       <c r="K102" s="3">
         <v>2098800</v>

--- a/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>TIIAY</t>
   </si>
@@ -656,353 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4468800</v>
+        <v>4247200</v>
       </c>
       <c r="E8" s="3">
-        <v>8537200</v>
+        <v>9131900</v>
       </c>
       <c r="F8" s="3">
-        <v>4185900</v>
+        <v>4438400</v>
       </c>
       <c r="G8" s="3">
-        <v>8956200</v>
+        <v>8479200</v>
       </c>
       <c r="H8" s="3">
-        <v>4321900</v>
+        <v>4157500</v>
       </c>
       <c r="I8" s="3">
+        <v>8895200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>4292500</v>
+      </c>
+      <c r="K8" s="3">
         <v>8222800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3965000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>8400700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>4089000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>8123100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>3969600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>8025100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4045700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>8464400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4324400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>10483300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>5425500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>10580500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>5348200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>11236400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>5134800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>10333300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>5144100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>11041500</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1848700</v>
+        <v>1755100</v>
       </c>
       <c r="E9" s="3">
-        <v>3505900</v>
+        <v>3962900</v>
       </c>
       <c r="F9" s="3">
-        <v>1709400</v>
+        <v>1836100</v>
       </c>
       <c r="G9" s="3">
-        <v>3892100</v>
+        <v>3482000</v>
       </c>
       <c r="H9" s="3">
-        <v>1801900</v>
+        <v>1697800</v>
       </c>
       <c r="I9" s="3">
+        <v>3865700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1789600</v>
+      </c>
+      <c r="K9" s="3">
         <v>3323100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1589700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3510300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1619700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3007800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1478000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3054000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1499800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2782900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1388700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>3552400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1755400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3517400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1818200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1594500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1979300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>6005000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1977500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1573400</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2620100</v>
+        <v>2492100</v>
       </c>
       <c r="E10" s="3">
-        <v>5031400</v>
+        <v>5169000</v>
       </c>
       <c r="F10" s="3">
-        <v>2476500</v>
+        <v>2602300</v>
       </c>
       <c r="G10" s="3">
-        <v>5064000</v>
+        <v>4997200</v>
       </c>
       <c r="H10" s="3">
-        <v>2520000</v>
+        <v>2459700</v>
       </c>
       <c r="I10" s="3">
+        <v>5029600</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2502900</v>
+      </c>
+      <c r="K10" s="3">
         <v>4899700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2375300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4890400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2469300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>5115300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2491600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>4971000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2546000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>5681500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2935600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>6930900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>3670100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>7063100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>3530000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>9641800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>3155600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>4328300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>3166600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>9468100</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1030,8 +1055,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1107,8 +1134,14 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,162 +1217,180 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>152300</v>
+        <v>95100</v>
       </c>
       <c r="E14" s="3">
-        <v>467900</v>
+        <v>220500</v>
       </c>
       <c r="F14" s="3">
-        <v>457000</v>
+        <v>151300</v>
       </c>
       <c r="G14" s="3">
-        <v>72900</v>
+        <v>464700</v>
       </c>
       <c r="H14" s="3">
-        <v>328600</v>
+        <v>453900</v>
       </c>
       <c r="I14" s="3">
+        <v>72400</v>
+      </c>
+      <c r="J14" s="3">
+        <v>326400</v>
+      </c>
+      <c r="K14" s="3">
         <v>317700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>77300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>4467600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>60300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>482500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>424300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>155600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>43600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>111300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>26200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>440100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>39200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-408200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>23900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>3320400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>2228500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>166900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>800400</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1321000</v>
+        <v>1301200</v>
       </c>
       <c r="E15" s="3">
-        <v>2643000</v>
+        <v>2630400</v>
       </c>
       <c r="F15" s="3">
-        <v>1306800</v>
+        <v>1312000</v>
       </c>
       <c r="G15" s="3">
-        <v>2700700</v>
+        <v>2625000</v>
       </c>
       <c r="H15" s="3">
-        <v>1354700</v>
+        <v>1297900</v>
       </c>
       <c r="I15" s="3">
+        <v>2682300</v>
+      </c>
+      <c r="J15" s="3">
+        <v>1345500</v>
+      </c>
+      <c r="K15" s="3">
         <v>2497200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>1204500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>2408900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>1230900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>2442400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>1195500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>2262100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1177000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>2561500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>1310200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>2838000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>1545900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>2936300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>1512000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>2523100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>1157400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>2330000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>1158400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>2442000</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1415,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4110800</v>
+        <v>4023400</v>
       </c>
       <c r="E17" s="3">
-        <v>8277200</v>
+        <v>8486700</v>
       </c>
       <c r="F17" s="3">
-        <v>4362200</v>
+        <v>4082900</v>
       </c>
       <c r="G17" s="3">
-        <v>8728700</v>
+        <v>8220900</v>
       </c>
       <c r="H17" s="3">
-        <v>4277300</v>
+        <v>4332500</v>
       </c>
       <c r="I17" s="3">
+        <v>8669400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4248200</v>
+      </c>
+      <c r="K17" s="3">
         <v>7790800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3737600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>12769600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3597900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>7601800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3922000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>6965800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3438600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>7327600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3742900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>8979700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4414900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>8360700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4531200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>12517400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>6272300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>8561100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>4329400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>9482300</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>358000</v>
+        <v>223700</v>
       </c>
       <c r="E18" s="3">
-        <v>260100</v>
+        <v>645200</v>
       </c>
       <c r="F18" s="3">
-        <v>-176300</v>
+        <v>355600</v>
       </c>
       <c r="G18" s="3">
+        <v>258300</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-175100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>225900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>44300</v>
+      </c>
+      <c r="K18" s="3">
+        <v>432000</v>
+      </c>
+      <c r="L18" s="3">
         <v>227400</v>
       </c>
-      <c r="H18" s="3">
-        <v>44600</v>
-      </c>
-      <c r="I18" s="3">
-        <v>432000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>227400</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4368900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>491100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>521200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>47600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1059200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>607200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1136700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>581500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1503600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1010600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>2219900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>817000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1281100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1137500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1772200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>814700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1559200</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,162 +1612,176 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-536400</v>
+        <v>-547900</v>
       </c>
       <c r="E20" s="3">
-        <v>-609300</v>
+        <v>-788900</v>
       </c>
       <c r="F20" s="3">
-        <v>-408000</v>
+        <v>-532800</v>
       </c>
       <c r="G20" s="3">
-        <v>167600</v>
+        <v>-605200</v>
       </c>
       <c r="H20" s="3">
-        <v>-236100</v>
+        <v>-405300</v>
       </c>
       <c r="I20" s="3">
+        <v>166400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-234500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-29400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-327500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>173500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-290800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>42000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-293100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>44900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-307200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>532400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>152700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-2300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-448300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-24700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-462900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>4700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-364400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-59300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-383200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-36200</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1142500</v>
+        <v>977000</v>
       </c>
       <c r="E21" s="3">
-        <v>2293700</v>
+        <v>2486700</v>
       </c>
       <c r="F21" s="3">
-        <v>722500</v>
+        <v>1134700</v>
       </c>
       <c r="G21" s="3">
-        <v>3095600</v>
+        <v>2278100</v>
       </c>
       <c r="H21" s="3">
-        <v>1163200</v>
+        <v>717600</v>
       </c>
       <c r="I21" s="3">
+        <v>3074600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1155300</v>
+      </c>
+      <c r="K21" s="3">
         <v>2899800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1104400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1786600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1432300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>3005600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>950100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>3366200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1476900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>4230500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>2044400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>4339300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>2108200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>5131500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1866100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1246800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-344500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>4042800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1589900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>3964900</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1710,230 +1789,248 @@
         <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>227400</v>
+        <v>234500</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="3">
-        <v>754100</v>
+        <v>225900</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I22" s="3">
-        <v>683300</v>
+        <v>748900</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K22" s="3">
-        <v>648300</v>
+        <v>683300</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M22" s="3">
-        <v>632100</v>
+        <v>648300</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="3">
-        <v>597400</v>
+        <v>632100</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q22" s="3">
-        <v>699300</v>
+        <v>597400</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S22" s="3">
-        <v>792700</v>
+        <v>699300</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U22" s="3">
-        <v>863500</v>
+        <v>792700</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W22" s="3">
-        <v>747600</v>
+        <v>863500</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y22" s="3">
-        <v>720300</v>
+        <v>747600</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA22" s="3">
+        <v>720300</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC22" s="3">
         <v>791700</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-178400</v>
+        <v>-324200</v>
       </c>
       <c r="E23" s="3">
-        <v>-576700</v>
+        <v>-378200</v>
       </c>
       <c r="F23" s="3">
-        <v>-584300</v>
+        <v>-177200</v>
       </c>
       <c r="G23" s="3">
-        <v>-359100</v>
+        <v>-572800</v>
       </c>
       <c r="H23" s="3">
-        <v>-191500</v>
+        <v>-580300</v>
       </c>
       <c r="I23" s="3">
+        <v>-356600</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-190200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-280700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-100100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4843800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>200300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-68900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-245500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>506700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>300000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>969800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>734200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>708600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>562300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1331700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>354100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-2023900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1501900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>992600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>431500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>731300</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>68600</v>
+        <v>45400</v>
       </c>
       <c r="E24" s="3">
-        <v>155600</v>
+        <v>90800</v>
       </c>
       <c r="F24" s="3">
-        <v>92500</v>
+        <v>68100</v>
       </c>
       <c r="G24" s="3">
-        <v>2137000</v>
+        <v>154500</v>
       </c>
       <c r="H24" s="3">
-        <v>2183800</v>
+        <v>91900</v>
       </c>
       <c r="I24" s="3">
+        <v>2122500</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2169000</v>
+      </c>
+      <c r="K24" s="3">
         <v>111000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>54400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>4213900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-38800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-7500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-40200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-6105100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-240800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>181100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>89500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>141300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>129800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>461100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>130400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>82800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-56500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>326100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>171300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>36200</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2106,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-247000</v>
+        <v>-369600</v>
       </c>
       <c r="E26" s="3">
-        <v>-732300</v>
+        <v>-469000</v>
       </c>
       <c r="F26" s="3">
-        <v>-676800</v>
+        <v>-245300</v>
       </c>
       <c r="G26" s="3">
-        <v>-2496100</v>
+        <v>-727300</v>
       </c>
       <c r="H26" s="3">
-        <v>-2375300</v>
+        <v>-672200</v>
       </c>
       <c r="I26" s="3">
+        <v>-2479100</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-2359200</v>
+      </c>
+      <c r="K26" s="3">
         <v>-391700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-154500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-9057700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>239100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-61400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-205300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>6611800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>540700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>788700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>644700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>567400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>432400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>870500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>223700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-2106700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1445400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>666500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>260200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-338400</v>
+        <v>-432300</v>
       </c>
       <c r="E27" s="3">
-        <v>-884600</v>
+        <v>-678700</v>
       </c>
       <c r="F27" s="3">
-        <v>-749700</v>
+        <v>-336100</v>
       </c>
       <c r="G27" s="3">
-        <v>-2657100</v>
+        <v>-878600</v>
       </c>
       <c r="H27" s="3">
-        <v>-2442800</v>
+        <v>-744600</v>
       </c>
       <c r="I27" s="3">
+        <v>-2639100</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-2426200</v>
+      </c>
+      <c r="K27" s="3">
         <v>-525600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-222000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-9231100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>149700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-160500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-228500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>6529000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>519000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>739600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>610900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>407400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>368700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>648200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>197400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-2324400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1575000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>584100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>220700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2278,27 +2399,27 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>18700</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
@@ -2317,8 +2438,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,162 +2604,180 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>536400</v>
+        <v>547900</v>
       </c>
       <c r="E32" s="3">
-        <v>609300</v>
+        <v>788900</v>
       </c>
       <c r="F32" s="3">
-        <v>408000</v>
+        <v>532800</v>
       </c>
       <c r="G32" s="3">
-        <v>-167600</v>
+        <v>605200</v>
       </c>
       <c r="H32" s="3">
-        <v>236100</v>
+        <v>405300</v>
       </c>
       <c r="I32" s="3">
+        <v>-166400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>234500</v>
+      </c>
+      <c r="K32" s="3">
         <v>29400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>327500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-173500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>290800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-42000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>293100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-44900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>307200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-532400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-152700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>2300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>448300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>24700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>462900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-4700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>364400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>59300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>383200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>36200</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-338400</v>
+        <v>-432300</v>
       </c>
       <c r="E33" s="3">
-        <v>-884600</v>
+        <v>-678700</v>
       </c>
       <c r="F33" s="3">
-        <v>-749700</v>
+        <v>-336100</v>
       </c>
       <c r="G33" s="3">
-        <v>-2657100</v>
+        <v>-878600</v>
       </c>
       <c r="H33" s="3">
-        <v>-2442800</v>
+        <v>-744600</v>
       </c>
       <c r="I33" s="3">
+        <v>-2639100</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-2426200</v>
+      </c>
+      <c r="K33" s="3">
         <v>-525600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-222000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-9231100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>149700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-160500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-228500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>6529000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>519000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>739600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>610900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>426100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>368700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>648200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>197400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-2324400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1575000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>584100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>220700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2853,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-338400</v>
+        <v>-432300</v>
       </c>
       <c r="E35" s="3">
-        <v>-884600</v>
+        <v>-678700</v>
       </c>
       <c r="F35" s="3">
-        <v>-749700</v>
+        <v>-336100</v>
       </c>
       <c r="G35" s="3">
-        <v>-2657100</v>
+        <v>-878600</v>
       </c>
       <c r="H35" s="3">
-        <v>-2442800</v>
+        <v>-744600</v>
       </c>
       <c r="I35" s="3">
+        <v>-2639100</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-2426200</v>
+      </c>
+      <c r="K35" s="3">
         <v>-525600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-222000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-9231100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>149700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-160500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-228500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>6529000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>519000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>739600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>610900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>426100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>368700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>648200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>197400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-2324400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1575000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>584100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>220700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,316 +3090,342 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3580900</v>
+        <v>1388700</v>
       </c>
       <c r="E41" s="3">
-        <v>2595100</v>
+        <v>3147000</v>
       </c>
       <c r="F41" s="3">
-        <v>2894300</v>
+        <v>3556600</v>
       </c>
       <c r="G41" s="3">
-        <v>3868200</v>
+        <v>2577500</v>
       </c>
       <c r="H41" s="3">
-        <v>3829000</v>
+        <v>2874700</v>
       </c>
       <c r="I41" s="3">
+        <v>3841900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>3803000</v>
+      </c>
+      <c r="K41" s="3">
         <v>2601600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3560300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7484600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4784700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>5351100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4623500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>4816400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2966300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3930500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3561800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3663300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2630100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1999900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2515600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2267600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2816600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2308000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1844600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>3925400</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1982500</v>
+        <v>2187300</v>
       </c>
       <c r="E42" s="3">
-        <v>2064100</v>
+        <v>2778500</v>
       </c>
       <c r="F42" s="3">
-        <v>1826900</v>
+        <v>1969000</v>
       </c>
       <c r="G42" s="3">
-        <v>1741000</v>
+        <v>2050100</v>
       </c>
       <c r="H42" s="3">
-        <v>2075000</v>
+        <v>1814500</v>
       </c>
       <c r="I42" s="3">
+        <v>1729100</v>
+      </c>
+      <c r="J42" s="3">
+        <v>2060900</v>
+      </c>
+      <c r="K42" s="3">
         <v>2048900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>2308900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>2592100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1643300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1573400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>3134900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1250700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1293200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>1098500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>1074500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>1166200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>1527600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>1307000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>1882800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1651300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>1694600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1564700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>1831500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1570100</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5437200</v>
+        <v>5863900</v>
       </c>
       <c r="E43" s="3">
-        <v>3784400</v>
+        <v>4091500</v>
       </c>
       <c r="F43" s="3">
-        <v>5175000</v>
+        <v>5400300</v>
       </c>
       <c r="G43" s="3">
-        <v>3881300</v>
+        <v>3758700</v>
       </c>
       <c r="H43" s="3">
-        <v>5351300</v>
+        <v>5139800</v>
       </c>
       <c r="I43" s="3">
+        <v>3854900</v>
+      </c>
+      <c r="J43" s="3">
+        <v>5314900</v>
+      </c>
+      <c r="K43" s="3">
         <v>3698500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4971500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3694600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4720100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3787500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4649900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3621600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4836600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>4119300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>5433800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>4973200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>6253600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>4826800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>6313500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>4907900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>5703000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>4508400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>5900700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>4597300</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>396100</v>
+        <v>419300</v>
       </c>
       <c r="E44" s="3">
-        <v>410200</v>
+        <v>372800</v>
       </c>
       <c r="F44" s="3">
-        <v>395000</v>
+        <v>393400</v>
       </c>
       <c r="G44" s="3">
-        <v>350400</v>
+        <v>407400</v>
       </c>
       <c r="H44" s="3">
-        <v>374300</v>
+        <v>392300</v>
       </c>
       <c r="I44" s="3">
+        <v>348000</v>
+      </c>
+      <c r="J44" s="3">
+        <v>371800</v>
+      </c>
+      <c r="K44" s="3">
         <v>352500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>336200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>305700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>385500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>366100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>350200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>286300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>282300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>279300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>307600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>303500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>366300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>371700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>388800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>460100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>344500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>352500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>357900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>318400</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3236,384 +3433,414 @@
         <v>8</v>
       </c>
       <c r="E45" s="3">
-        <v>1551600</v>
+        <v>1368200</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="3">
-        <v>1292700</v>
+        <v>1541100</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I45" s="3">
-        <v>1360100</v>
+        <v>1283900</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K45" s="3">
-        <v>1176200</v>
+        <v>1360100</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M45" s="3">
-        <v>1005800</v>
+        <v>1176200</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O45" s="3">
-        <v>853800</v>
+        <v>1005800</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q45" s="3">
-        <v>1030900</v>
+        <v>853800</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S45" s="3">
-        <v>938600</v>
+        <v>1030900</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U45" s="3">
-        <v>1203500</v>
+        <v>938600</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W45" s="3">
-        <v>1038600</v>
+        <v>1203500</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y45" s="3">
-        <v>1109000</v>
+        <v>1038600</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA45" s="3">
+        <v>1109000</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3">
         <v>932200</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>11396800</v>
+        <v>9859200</v>
       </c>
       <c r="E46" s="3">
-        <v>10405500</v>
+        <v>11758000</v>
       </c>
       <c r="F46" s="3">
-        <v>10291200</v>
+        <v>11319300</v>
       </c>
       <c r="G46" s="3">
-        <v>11133400</v>
+        <v>10334700</v>
       </c>
       <c r="H46" s="3">
-        <v>11629600</v>
+        <v>10221300</v>
       </c>
       <c r="I46" s="3">
+        <v>11057700</v>
+      </c>
+      <c r="J46" s="3">
+        <v>11550500</v>
+      </c>
+      <c r="K46" s="3">
         <v>10061700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>11177000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>15253300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>11533600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>12083900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>12758400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10762900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>9378500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>10458600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>10377800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>11044900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>10777500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>9708800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>11100700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>10325500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>10558800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>9842500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>9934700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>11343400</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4537400</v>
+        <v>4386600</v>
       </c>
       <c r="E47" s="3">
-        <v>1828000</v>
+        <v>1420000</v>
       </c>
       <c r="F47" s="3">
-        <v>5157600</v>
+        <v>4506500</v>
       </c>
       <c r="G47" s="3">
-        <v>1557100</v>
+        <v>1815600</v>
       </c>
       <c r="H47" s="3">
-        <v>5613500</v>
+        <v>5122500</v>
       </c>
       <c r="I47" s="3">
+        <v>1546500</v>
+      </c>
+      <c r="J47" s="3">
+        <v>5575300</v>
+      </c>
+      <c r="K47" s="3">
         <v>1270900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>8292400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>4296300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>7922800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>3883300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>7397500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>3628500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>7896300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>4272000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>9769100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>3208000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>6742300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>3669200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>5077900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>2973800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>3953000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>2599000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>4036200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>3033800</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>21438800</v>
+        <v>21789100</v>
       </c>
       <c r="E48" s="3">
-        <v>21566100</v>
+        <v>21837700</v>
       </c>
       <c r="F48" s="3">
-        <v>21369200</v>
+        <v>21293000</v>
       </c>
       <c r="G48" s="3">
-        <v>21313700</v>
+        <v>21419500</v>
       </c>
       <c r="H48" s="3">
-        <v>21260400</v>
+        <v>21223900</v>
       </c>
       <c r="I48" s="3">
+        <v>21168800</v>
+      </c>
+      <c r="J48" s="3">
+        <v>21115800</v>
+      </c>
+      <c r="K48" s="3">
         <v>21245200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>20531400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>19685100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>19160200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>19327100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>18865200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>18085900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>18349000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>19645100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>20250600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>22770300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>24117600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>23400900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>23709900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>19099100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>17481300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>17492200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>17704200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>18168600</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>28757400</v>
+        <v>28231100</v>
       </c>
       <c r="E49" s="3">
-        <v>29030500</v>
+        <v>28413800</v>
       </c>
       <c r="F49" s="3">
-        <v>29014200</v>
+        <v>28561800</v>
       </c>
       <c r="G49" s="3">
-        <v>29125200</v>
+        <v>28833100</v>
       </c>
       <c r="H49" s="3">
-        <v>29301400</v>
+        <v>28816900</v>
       </c>
       <c r="I49" s="3">
+        <v>28927100</v>
+      </c>
+      <c r="J49" s="3">
+        <v>29102200</v>
+      </c>
+      <c r="K49" s="3">
         <v>29278600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>28359200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>27877600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>31416400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>31655500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>30996200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>29510100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>30568200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>32440400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>32756800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>35897900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>42218100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>40927000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>41849100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>42179800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>37227500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>39297400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>39766300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>40246100</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,85 +3999,97 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>860700</v>
+        <v>756500</v>
       </c>
       <c r="E52" s="3">
-        <v>3901900</v>
+        <v>3745700</v>
       </c>
       <c r="F52" s="3">
-        <v>847600</v>
+        <v>854800</v>
       </c>
       <c r="G52" s="3">
-        <v>4362200</v>
+        <v>3875400</v>
       </c>
       <c r="H52" s="3">
-        <v>861800</v>
+        <v>841900</v>
       </c>
       <c r="I52" s="3">
+        <v>4332500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>855900</v>
+      </c>
+      <c r="K52" s="3">
         <v>10577400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3775700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>7893300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>8560300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>12529700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>7984700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>11035200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1120900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>5791600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1022200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>8919000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1248300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3597400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1498800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>3106300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1190700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2232200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>991500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2731800</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4165,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>66991100</v>
+        <v>65022500</v>
       </c>
       <c r="E54" s="3">
-        <v>66732100</v>
+        <v>67175200</v>
       </c>
       <c r="F54" s="3">
-        <v>66679900</v>
+        <v>66535500</v>
       </c>
       <c r="G54" s="3">
-        <v>67491600</v>
+        <v>66278300</v>
       </c>
       <c r="H54" s="3">
-        <v>68666700</v>
+        <v>66226400</v>
       </c>
       <c r="I54" s="3">
+        <v>67032600</v>
+      </c>
+      <c r="J54" s="3">
+        <v>68199700</v>
+      </c>
+      <c r="K54" s="3">
         <v>72433700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>72135600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>75005600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>78593200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>79479500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>78002100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>73022600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>67313000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>72607700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>74176400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>81840100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>85103700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>81303400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>83236400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>77620700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>70411200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>71463300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>72432900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>75523700</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,470 +4314,508 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8589500</v>
+        <v>9783600</v>
       </c>
       <c r="E57" s="3">
-        <v>5235900</v>
+        <v>5880100</v>
       </c>
       <c r="F57" s="3">
-        <v>8725500</v>
+        <v>8531000</v>
       </c>
       <c r="G57" s="3">
-        <v>5761500</v>
+        <v>5200300</v>
       </c>
       <c r="H57" s="3">
-        <v>8259800</v>
+        <v>8666100</v>
       </c>
       <c r="I57" s="3">
+        <v>5722300</v>
+      </c>
+      <c r="J57" s="3">
+        <v>8203600</v>
+      </c>
+      <c r="K57" s="3">
         <v>4971500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>10505600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>5595000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>8740100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>4093300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>7438800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4122300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>6131900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>3279300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>7170600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5046700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>7912200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>4031500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>8182000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>5287600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>6761900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>3978100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>7476300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>5100200</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7554700</v>
+        <v>5926600</v>
       </c>
       <c r="E58" s="3">
-        <v>8930000</v>
+        <v>7014800</v>
       </c>
       <c r="F58" s="3">
-        <v>6536200</v>
+        <v>7503300</v>
       </c>
       <c r="G58" s="3">
-        <v>6126000</v>
+        <v>8869300</v>
       </c>
       <c r="H58" s="3">
-        <v>6108600</v>
+        <v>6491800</v>
       </c>
       <c r="I58" s="3">
+        <v>6084300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>6067000</v>
+      </c>
+      <c r="K58" s="3">
         <v>4662500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>4146700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>7044500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>5442700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>5541700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>6075000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>4233000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>4583400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>4700700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>4584000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>4388300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>5239300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>4011500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>6679600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>6594700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>7155100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>6297000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>5512000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>5139700</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>26100</v>
+        <v>24900</v>
       </c>
       <c r="E59" s="3">
-        <v>3833400</v>
+        <v>4417900</v>
       </c>
       <c r="F59" s="3">
-        <v>46800</v>
+        <v>25900</v>
       </c>
       <c r="G59" s="3">
-        <v>3500400</v>
+        <v>3807300</v>
       </c>
       <c r="H59" s="3">
-        <v>9800</v>
+        <v>46500</v>
       </c>
       <c r="I59" s="3">
+        <v>3476600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>9700</v>
+      </c>
+      <c r="K59" s="3">
         <v>5817000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>297100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5100700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>261700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3603300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>269800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2761800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>58100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3511600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>46900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>3550100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>51400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>3972700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>77800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>3354700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>47600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>3631100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>81300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>3362100</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>16170300</v>
+        <v>15735000</v>
       </c>
       <c r="E60" s="3">
-        <v>17999400</v>
+        <v>17312800</v>
       </c>
       <c r="F60" s="3">
-        <v>15308500</v>
+        <v>16060300</v>
       </c>
       <c r="G60" s="3">
-        <v>15387900</v>
+        <v>17876900</v>
       </c>
       <c r="H60" s="3">
-        <v>14378200</v>
+        <v>15204400</v>
       </c>
       <c r="I60" s="3">
+        <v>15283300</v>
+      </c>
+      <c r="J60" s="3">
+        <v>14280400</v>
+      </c>
+      <c r="K60" s="3">
         <v>15451000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>14949400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>17740200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>14444500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>13238300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>13783600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>11117000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>10773400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>11491600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>11801500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>12985100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>13202900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>12015700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>14939300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>15236900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>13964600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>13906200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>13069500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>13602000</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>28254700</v>
+        <v>28045200</v>
       </c>
       <c r="E61" s="3">
-        <v>25280900</v>
+        <v>27678900</v>
       </c>
       <c r="F61" s="3">
-        <v>28139400</v>
+        <v>28062500</v>
       </c>
       <c r="G61" s="3">
-        <v>28354800</v>
+        <v>25109000</v>
       </c>
       <c r="H61" s="3">
-        <v>29929300</v>
+        <v>27948000</v>
       </c>
       <c r="I61" s="3">
+        <v>28162000</v>
+      </c>
+      <c r="J61" s="3">
+        <v>29725700</v>
+      </c>
+      <c r="K61" s="3">
         <v>28256900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>28920600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>28346000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>27642900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>26142800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>26892200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>25944400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>28929400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>29868000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>32482900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>33295700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>37070600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>33809700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>35096500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>27956700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>27723200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>25709700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>28833500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>28755500</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3195700</v>
+        <v>2862800</v>
       </c>
       <c r="E62" s="3">
-        <v>3578800</v>
+        <v>3257200</v>
       </c>
       <c r="F62" s="3">
-        <v>3462300</v>
+        <v>3174000</v>
       </c>
       <c r="G62" s="3">
-        <v>3374200</v>
+        <v>3554400</v>
       </c>
       <c r="H62" s="3">
-        <v>3521100</v>
+        <v>3438800</v>
       </c>
       <c r="I62" s="3">
+        <v>3351300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>3497100</v>
+      </c>
+      <c r="K62" s="3">
         <v>4216400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3527600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>5027000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3509600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>7147400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>5774600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>7196200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>5323400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>7909100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>5880000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>9145500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>7214000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>9204200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>7100600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>8702600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>4465800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>6158700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>4571000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>7052500</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,85 +5057,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>51766400</v>
+        <v>50760500</v>
       </c>
       <c r="E66" s="3">
-        <v>51033000</v>
+        <v>52428000</v>
       </c>
       <c r="F66" s="3">
-        <v>50942700</v>
+        <v>51414300</v>
       </c>
       <c r="G66" s="3">
-        <v>51103700</v>
+        <v>50685900</v>
       </c>
       <c r="H66" s="3">
-        <v>51843600</v>
+        <v>50596200</v>
       </c>
       <c r="I66" s="3">
+        <v>50756200</v>
+      </c>
+      <c r="J66" s="3">
+        <v>51491000</v>
+      </c>
+      <c r="K66" s="3">
         <v>53294000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>52782600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>56127100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>50548600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>51473700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>51146900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>46875800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>46319400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>50701100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>51678600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>58165000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>60332000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>57835400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>59776500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>54521000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>48500700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>48032000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>48898300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>51854100</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5503,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4256600</v>
+        <v>3444200</v>
       </c>
       <c r="E72" s="3">
-        <v>4578700</v>
+        <v>3880800</v>
       </c>
       <c r="F72" s="3">
-        <v>3012900</v>
+        <v>4227700</v>
       </c>
       <c r="G72" s="3">
-        <v>3768100</v>
+        <v>4547600</v>
       </c>
       <c r="H72" s="3">
-        <v>3967200</v>
+        <v>2992500</v>
       </c>
       <c r="I72" s="3">
+        <v>3742500</v>
+      </c>
+      <c r="J72" s="3">
+        <v>3940200</v>
+      </c>
+      <c r="K72" s="3">
         <v>6418700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>6722300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>6912200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>16264400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>16093200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>15713400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>15440700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>9793600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>9747300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>9963300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>9994200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>10410000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>9644100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>9345900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>9238400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>9251800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>10729700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>10540800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>10403600</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5835,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>15224700</v>
+        <v>14262000</v>
       </c>
       <c r="E76" s="3">
-        <v>15699100</v>
+        <v>14747200</v>
       </c>
       <c r="F76" s="3">
-        <v>15737200</v>
+        <v>15121200</v>
       </c>
       <c r="G76" s="3">
-        <v>16387900</v>
+        <v>15592300</v>
       </c>
       <c r="H76" s="3">
-        <v>16823100</v>
+        <v>15630200</v>
       </c>
       <c r="I76" s="3">
+        <v>16276400</v>
+      </c>
+      <c r="J76" s="3">
+        <v>16708700</v>
+      </c>
+      <c r="K76" s="3">
         <v>19139700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>19352900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>18878500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>28044600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>28005900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>26855200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>26146800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>20993600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>21906600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>22497800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>23675100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>24771700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>23468000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>23459900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>23099700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>21910500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>23431300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>23534500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>23669600</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +6001,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-338400</v>
+        <v>-432300</v>
       </c>
       <c r="E81" s="3">
-        <v>-884600</v>
+        <v>-678700</v>
       </c>
       <c r="F81" s="3">
-        <v>-749700</v>
+        <v>-336100</v>
       </c>
       <c r="G81" s="3">
-        <v>-2657100</v>
+        <v>-878600</v>
       </c>
       <c r="H81" s="3">
-        <v>-2442800</v>
+        <v>-744600</v>
       </c>
       <c r="I81" s="3">
+        <v>-2639100</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-2426200</v>
+      </c>
+      <c r="K81" s="3">
         <v>-525600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-222000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-9231100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>149700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-160500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-228500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>6529000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>519000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>739600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>610900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>426100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>368700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>648200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>197400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-2324400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1575000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>584100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>220700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,85 +6207,93 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1321000</v>
+        <v>1301200</v>
       </c>
       <c r="E83" s="3">
-        <v>2643000</v>
+        <v>2630400</v>
       </c>
       <c r="F83" s="3">
-        <v>1306800</v>
+        <v>1312000</v>
       </c>
       <c r="G83" s="3">
-        <v>2700700</v>
+        <v>2625000</v>
       </c>
       <c r="H83" s="3">
-        <v>1354700</v>
+        <v>1297900</v>
       </c>
       <c r="I83" s="3">
+        <v>2682300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1345500</v>
+      </c>
+      <c r="K83" s="3">
         <v>2497200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1204500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>2408900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1232000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>2442400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1195500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>2262100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1177000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>2561500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1310200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>2838000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1545900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>2936300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1512000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>2523100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1157400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>2330000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>1158400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>2442000</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6701,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>872700</v>
+        <v>416100</v>
       </c>
       <c r="E89" s="3">
-        <v>1885700</v>
+        <v>2389400</v>
       </c>
       <c r="F89" s="3">
-        <v>926000</v>
+        <v>866700</v>
       </c>
       <c r="G89" s="3">
-        <v>2613600</v>
+        <v>1872900</v>
       </c>
       <c r="H89" s="3">
-        <v>1101200</v>
+        <v>919700</v>
       </c>
       <c r="I89" s="3">
+        <v>2595800</v>
+      </c>
+      <c r="J89" s="3">
+        <v>1093700</v>
+      </c>
+      <c r="K89" s="3">
         <v>2712600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1169700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2613800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1117800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2073000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1334100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2514400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1574500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>4396400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>2585500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>3281600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1699100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>3692700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1776400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>2382400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1032300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>2830600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1021100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>2482600</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,85 +6819,93 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1076000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1207000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-789000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-919000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1054000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1003000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2713000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1438000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1151000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2364000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-872000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1187000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-924700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1275700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2787800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-90500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-1239300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-1778000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-937100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-2501000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-61000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-2622500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-75300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-674200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-536900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-3041500</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +7064,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-958600</v>
+        <v>-705700</v>
       </c>
       <c r="E94" s="3">
-        <v>-2338300</v>
+        <v>-2161400</v>
       </c>
       <c r="F94" s="3">
-        <v>-1256800</v>
+        <v>-952100</v>
       </c>
       <c r="G94" s="3">
-        <v>-2514600</v>
+        <v>-2322400</v>
       </c>
       <c r="H94" s="3">
-        <v>-1669100</v>
+        <v>-1248200</v>
       </c>
       <c r="I94" s="3">
+        <v>-2497500</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1657800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-3290400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-822600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-3139600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1165200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-2391800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-889800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1457200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-994300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1762900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1220700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1480300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1075500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-2337500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1498800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-2488800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-1073300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-2426600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1653600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-2909700</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,85 +7182,93 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-84900</v>
+        <v>-42100</v>
       </c>
       <c r="E96" s="3">
-        <v>-93600</v>
+        <v>-111300</v>
       </c>
       <c r="F96" s="3">
-        <v>-41300</v>
+        <v>-84300</v>
       </c>
       <c r="G96" s="3">
-        <v>-33700</v>
+        <v>-92900</v>
       </c>
       <c r="H96" s="3">
-        <v>-17400</v>
+        <v>-41100</v>
       </c>
       <c r="I96" s="3">
+        <v>-33500</v>
+      </c>
+      <c r="J96" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="K96" s="3">
         <v>-40300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-28300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-34700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-19400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-361800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-25400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-33900</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-388400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-43600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-38500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-7300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-289400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-29900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-40200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-243800</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-18700</v>
       </c>
     </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,235 +7510,259 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1074000</v>
+        <v>-1464300</v>
       </c>
       <c r="E100" s="3">
-        <v>-856300</v>
+        <v>357700</v>
       </c>
       <c r="F100" s="3">
-        <v>-648500</v>
+        <v>1066700</v>
       </c>
       <c r="G100" s="3">
-        <v>1199100</v>
+        <v>-850500</v>
       </c>
       <c r="H100" s="3">
-        <v>1792100</v>
+        <v>-644100</v>
       </c>
       <c r="I100" s="3">
+        <v>1190900</v>
+      </c>
+      <c r="J100" s="3">
+        <v>1779900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-4320800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-4462300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>2662500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-483500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>762400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-576600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-144600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1498700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-2033500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1206500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-29200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-128600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1281100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>279900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-432900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>548300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-1607500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-1103500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-429300</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-5400</v>
       </c>
-      <c r="E101" s="3">
-        <v>35900</v>
-      </c>
-      <c r="F101" s="3">
-        <v>4400</v>
-      </c>
       <c r="G101" s="3">
-        <v>-22900</v>
+        <v>35700</v>
       </c>
       <c r="H101" s="3">
-        <v>12000</v>
+        <v>4300</v>
       </c>
       <c r="I101" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="J101" s="3">
+        <v>11900</v>
+      </c>
+      <c r="K101" s="3">
         <v>-20700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>156700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-37900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-37700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>51700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-14800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-9000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-163600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-90500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-17500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-3700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>5900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>7200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-14200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-16600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-56000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-65900</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>982600</v>
+        <v>-1758300</v>
       </c>
       <c r="E102" s="3">
-        <v>-1273100</v>
+        <v>569500</v>
       </c>
       <c r="F102" s="3">
-        <v>-974900</v>
+        <v>975900</v>
       </c>
       <c r="G102" s="3">
-        <v>1275300</v>
+        <v>-1264400</v>
       </c>
       <c r="H102" s="3">
-        <v>1236100</v>
+        <v>-968300</v>
       </c>
       <c r="I102" s="3">
+        <v>1266600</v>
+      </c>
+      <c r="J102" s="3">
+        <v>1227700</v>
+      </c>
+      <c r="K102" s="3">
         <v>-4919300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3958500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>2098800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-568600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>495400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-147100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>903600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-927900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>436400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>67600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1754600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>491200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>80000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>564600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-553600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>490700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1259400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1756800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-922300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
@@ -783,25 +783,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4247200</v>
+        <v>4352900</v>
       </c>
       <c r="E8" s="3">
-        <v>9131900</v>
+        <v>9359200</v>
       </c>
       <c r="F8" s="3">
-        <v>4438400</v>
+        <v>4548900</v>
       </c>
       <c r="G8" s="3">
-        <v>8479200</v>
+        <v>8690200</v>
       </c>
       <c r="H8" s="3">
-        <v>4157500</v>
+        <v>4260900</v>
       </c>
       <c r="I8" s="3">
-        <v>8895200</v>
+        <v>9116700</v>
       </c>
       <c r="J8" s="3">
-        <v>4292500</v>
+        <v>4399400</v>
       </c>
       <c r="K8" s="3">
         <v>8222800</v>
@@ -866,25 +866,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1755100</v>
+        <v>1798700</v>
       </c>
       <c r="E9" s="3">
-        <v>3962900</v>
+        <v>4061600</v>
       </c>
       <c r="F9" s="3">
-        <v>1836100</v>
+        <v>1881800</v>
       </c>
       <c r="G9" s="3">
-        <v>3482000</v>
+        <v>3568700</v>
       </c>
       <c r="H9" s="3">
-        <v>1697800</v>
+        <v>1740000</v>
       </c>
       <c r="I9" s="3">
-        <v>3865700</v>
+        <v>3961900</v>
       </c>
       <c r="J9" s="3">
-        <v>1789600</v>
+        <v>1834200</v>
       </c>
       <c r="K9" s="3">
         <v>3323100</v>
@@ -949,25 +949,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2492100</v>
+        <v>2554100</v>
       </c>
       <c r="E10" s="3">
-        <v>5169000</v>
+        <v>5297700</v>
       </c>
       <c r="F10" s="3">
-        <v>2602300</v>
+        <v>2667100</v>
       </c>
       <c r="G10" s="3">
-        <v>4997200</v>
+        <v>5121500</v>
       </c>
       <c r="H10" s="3">
-        <v>2459700</v>
+        <v>2520900</v>
       </c>
       <c r="I10" s="3">
-        <v>5029600</v>
+        <v>5154800</v>
       </c>
       <c r="J10" s="3">
-        <v>2502900</v>
+        <v>2565200</v>
       </c>
       <c r="K10" s="3">
         <v>4899700</v>
@@ -1229,25 +1229,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>95100</v>
+        <v>97500</v>
       </c>
       <c r="E14" s="3">
-        <v>220500</v>
+        <v>226000</v>
       </c>
       <c r="F14" s="3">
-        <v>151300</v>
+        <v>155100</v>
       </c>
       <c r="G14" s="3">
-        <v>464700</v>
+        <v>476300</v>
       </c>
       <c r="H14" s="3">
-        <v>453900</v>
+        <v>465200</v>
       </c>
       <c r="I14" s="3">
-        <v>72400</v>
+        <v>74200</v>
       </c>
       <c r="J14" s="3">
-        <v>326400</v>
+        <v>334500</v>
       </c>
       <c r="K14" s="3">
         <v>317700</v>
@@ -1312,25 +1312,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1301200</v>
+        <v>1333600</v>
       </c>
       <c r="E15" s="3">
-        <v>2630400</v>
+        <v>2695900</v>
       </c>
       <c r="F15" s="3">
-        <v>1312000</v>
+        <v>1344600</v>
       </c>
       <c r="G15" s="3">
-        <v>2625000</v>
+        <v>2690400</v>
       </c>
       <c r="H15" s="3">
-        <v>1297900</v>
+        <v>1330200</v>
       </c>
       <c r="I15" s="3">
-        <v>2682300</v>
+        <v>2749100</v>
       </c>
       <c r="J15" s="3">
-        <v>1345500</v>
+        <v>1379000</v>
       </c>
       <c r="K15" s="3">
         <v>2497200</v>
@@ -1423,25 +1423,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4023400</v>
+        <v>4123600</v>
       </c>
       <c r="E17" s="3">
-        <v>8486700</v>
+        <v>8698000</v>
       </c>
       <c r="F17" s="3">
-        <v>4082900</v>
+        <v>4184500</v>
       </c>
       <c r="G17" s="3">
-        <v>8220900</v>
+        <v>8425500</v>
       </c>
       <c r="H17" s="3">
-        <v>4332500</v>
+        <v>4440400</v>
       </c>
       <c r="I17" s="3">
-        <v>8669400</v>
+        <v>8885200</v>
       </c>
       <c r="J17" s="3">
-        <v>4248200</v>
+        <v>4354000</v>
       </c>
       <c r="K17" s="3">
         <v>7790800</v>
@@ -1506,25 +1506,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>223700</v>
+        <v>229300</v>
       </c>
       <c r="E18" s="3">
-        <v>645200</v>
+        <v>661200</v>
       </c>
       <c r="F18" s="3">
-        <v>355600</v>
+        <v>364400</v>
       </c>
       <c r="G18" s="3">
-        <v>258300</v>
+        <v>264700</v>
       </c>
       <c r="H18" s="3">
-        <v>-175100</v>
+        <v>-179400</v>
       </c>
       <c r="I18" s="3">
-        <v>225900</v>
+        <v>231500</v>
       </c>
       <c r="J18" s="3">
-        <v>44300</v>
+        <v>45400</v>
       </c>
       <c r="K18" s="3">
         <v>432000</v>
@@ -1620,25 +1620,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-547900</v>
+        <v>-561600</v>
       </c>
       <c r="E20" s="3">
-        <v>-788900</v>
+        <v>-808500</v>
       </c>
       <c r="F20" s="3">
-        <v>-532800</v>
+        <v>-546000</v>
       </c>
       <c r="G20" s="3">
-        <v>-605200</v>
+        <v>-620300</v>
       </c>
       <c r="H20" s="3">
-        <v>-405300</v>
+        <v>-415400</v>
       </c>
       <c r="I20" s="3">
-        <v>166400</v>
+        <v>170600</v>
       </c>
       <c r="J20" s="3">
-        <v>-234500</v>
+        <v>-240300</v>
       </c>
       <c r="K20" s="3">
         <v>-29400</v>
@@ -1703,25 +1703,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>977000</v>
+        <v>1001300</v>
       </c>
       <c r="E21" s="3">
-        <v>2486700</v>
+        <v>2548600</v>
       </c>
       <c r="F21" s="3">
-        <v>1134700</v>
+        <v>1163000</v>
       </c>
       <c r="G21" s="3">
-        <v>2278100</v>
+        <v>2334800</v>
       </c>
       <c r="H21" s="3">
-        <v>717600</v>
+        <v>735400</v>
       </c>
       <c r="I21" s="3">
-        <v>3074600</v>
+        <v>3151100</v>
       </c>
       <c r="J21" s="3">
-        <v>1155300</v>
+        <v>1184000</v>
       </c>
       <c r="K21" s="3">
         <v>2899800</v>
@@ -1789,19 +1789,19 @@
         <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>234500</v>
+        <v>240300</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="3">
-        <v>225900</v>
+        <v>231500</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I22" s="3">
-        <v>748900</v>
+        <v>767600</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>8</v>
@@ -1869,25 +1869,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-324200</v>
+        <v>-332300</v>
       </c>
       <c r="E23" s="3">
-        <v>-378200</v>
+        <v>-387700</v>
       </c>
       <c r="F23" s="3">
-        <v>-177200</v>
+        <v>-181600</v>
       </c>
       <c r="G23" s="3">
-        <v>-572800</v>
+        <v>-587000</v>
       </c>
       <c r="H23" s="3">
-        <v>-580300</v>
+        <v>-594800</v>
       </c>
       <c r="I23" s="3">
-        <v>-356600</v>
+        <v>-365500</v>
       </c>
       <c r="J23" s="3">
-        <v>-190200</v>
+        <v>-194900</v>
       </c>
       <c r="K23" s="3">
         <v>-280700</v>
@@ -1952,25 +1952,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>45400</v>
+        <v>46500</v>
       </c>
       <c r="E24" s="3">
-        <v>90800</v>
+        <v>93000</v>
       </c>
       <c r="F24" s="3">
-        <v>68100</v>
+        <v>69800</v>
       </c>
       <c r="G24" s="3">
-        <v>154500</v>
+        <v>158400</v>
       </c>
       <c r="H24" s="3">
-        <v>91900</v>
+        <v>94100</v>
       </c>
       <c r="I24" s="3">
-        <v>2122500</v>
+        <v>2175300</v>
       </c>
       <c r="J24" s="3">
-        <v>2169000</v>
+        <v>2223000</v>
       </c>
       <c r="K24" s="3">
         <v>111000</v>
@@ -2118,25 +2118,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-369600</v>
+        <v>-378800</v>
       </c>
       <c r="E26" s="3">
-        <v>-469000</v>
+        <v>-480700</v>
       </c>
       <c r="F26" s="3">
-        <v>-245300</v>
+        <v>-251400</v>
       </c>
       <c r="G26" s="3">
-        <v>-727300</v>
+        <v>-745400</v>
       </c>
       <c r="H26" s="3">
-        <v>-672200</v>
+        <v>-688900</v>
       </c>
       <c r="I26" s="3">
-        <v>-2479100</v>
+        <v>-2540800</v>
       </c>
       <c r="J26" s="3">
-        <v>-2359200</v>
+        <v>-2417900</v>
       </c>
       <c r="K26" s="3">
         <v>-391700</v>
@@ -2201,25 +2201,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-432300</v>
+        <v>-443000</v>
       </c>
       <c r="E27" s="3">
-        <v>-678700</v>
+        <v>-695600</v>
       </c>
       <c r="F27" s="3">
-        <v>-336100</v>
+        <v>-344500</v>
       </c>
       <c r="G27" s="3">
-        <v>-878600</v>
+        <v>-900500</v>
       </c>
       <c r="H27" s="3">
-        <v>-744600</v>
+        <v>-763100</v>
       </c>
       <c r="I27" s="3">
-        <v>-2639100</v>
+        <v>-2704800</v>
       </c>
       <c r="J27" s="3">
-        <v>-2426200</v>
+        <v>-2486600</v>
       </c>
       <c r="K27" s="3">
         <v>-525600</v>
@@ -2616,25 +2616,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>547900</v>
+        <v>561600</v>
       </c>
       <c r="E32" s="3">
-        <v>788900</v>
+        <v>808500</v>
       </c>
       <c r="F32" s="3">
-        <v>532800</v>
+        <v>546000</v>
       </c>
       <c r="G32" s="3">
-        <v>605200</v>
+        <v>620300</v>
       </c>
       <c r="H32" s="3">
-        <v>405300</v>
+        <v>415400</v>
       </c>
       <c r="I32" s="3">
-        <v>-166400</v>
+        <v>-170600</v>
       </c>
       <c r="J32" s="3">
-        <v>234500</v>
+        <v>240300</v>
       </c>
       <c r="K32" s="3">
         <v>29400</v>
@@ -2699,25 +2699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-432300</v>
+        <v>-443000</v>
       </c>
       <c r="E33" s="3">
-        <v>-678700</v>
+        <v>-695600</v>
       </c>
       <c r="F33" s="3">
-        <v>-336100</v>
+        <v>-344500</v>
       </c>
       <c r="G33" s="3">
-        <v>-878600</v>
+        <v>-900500</v>
       </c>
       <c r="H33" s="3">
-        <v>-744600</v>
+        <v>-763100</v>
       </c>
       <c r="I33" s="3">
-        <v>-2639100</v>
+        <v>-2704800</v>
       </c>
       <c r="J33" s="3">
-        <v>-2426200</v>
+        <v>-2486600</v>
       </c>
       <c r="K33" s="3">
         <v>-525600</v>
@@ -2865,25 +2865,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-432300</v>
+        <v>-443000</v>
       </c>
       <c r="E35" s="3">
-        <v>-678700</v>
+        <v>-695600</v>
       </c>
       <c r="F35" s="3">
-        <v>-336100</v>
+        <v>-344500</v>
       </c>
       <c r="G35" s="3">
-        <v>-878600</v>
+        <v>-900500</v>
       </c>
       <c r="H35" s="3">
-        <v>-744600</v>
+        <v>-763100</v>
       </c>
       <c r="I35" s="3">
-        <v>-2639100</v>
+        <v>-2704800</v>
       </c>
       <c r="J35" s="3">
-        <v>-2426200</v>
+        <v>-2486600</v>
       </c>
       <c r="K35" s="3">
         <v>-525600</v>
@@ -3098,25 +3098,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1388700</v>
+        <v>1423300</v>
       </c>
       <c r="E41" s="3">
-        <v>3147000</v>
+        <v>3225300</v>
       </c>
       <c r="F41" s="3">
-        <v>3556600</v>
+        <v>3645100</v>
       </c>
       <c r="G41" s="3">
-        <v>2577500</v>
+        <v>2641600</v>
       </c>
       <c r="H41" s="3">
-        <v>2874700</v>
+        <v>2946200</v>
       </c>
       <c r="I41" s="3">
-        <v>3841900</v>
+        <v>3937500</v>
       </c>
       <c r="J41" s="3">
-        <v>3803000</v>
+        <v>3897600</v>
       </c>
       <c r="K41" s="3">
         <v>2601600</v>
@@ -3181,25 +3181,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2187300</v>
+        <v>2241800</v>
       </c>
       <c r="E42" s="3">
-        <v>2778500</v>
+        <v>2847600</v>
       </c>
       <c r="F42" s="3">
-        <v>1969000</v>
+        <v>2018000</v>
       </c>
       <c r="G42" s="3">
-        <v>2050100</v>
+        <v>2101100</v>
       </c>
       <c r="H42" s="3">
-        <v>1814500</v>
+        <v>1859700</v>
       </c>
       <c r="I42" s="3">
-        <v>1729100</v>
+        <v>1772200</v>
       </c>
       <c r="J42" s="3">
-        <v>2060900</v>
+        <v>2112200</v>
       </c>
       <c r="K42" s="3">
         <v>2048900</v>
@@ -3264,25 +3264,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5863900</v>
+        <v>6009800</v>
       </c>
       <c r="E43" s="3">
-        <v>4091500</v>
+        <v>4193400</v>
       </c>
       <c r="F43" s="3">
-        <v>5400300</v>
+        <v>5534700</v>
       </c>
       <c r="G43" s="3">
-        <v>3758700</v>
+        <v>3852200</v>
       </c>
       <c r="H43" s="3">
-        <v>5139800</v>
+        <v>5267700</v>
       </c>
       <c r="I43" s="3">
-        <v>3854900</v>
+        <v>3950800</v>
       </c>
       <c r="J43" s="3">
-        <v>5314900</v>
+        <v>5447200</v>
       </c>
       <c r="K43" s="3">
         <v>3698500</v>
@@ -3347,25 +3347,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>419300</v>
+        <v>429700</v>
       </c>
       <c r="E44" s="3">
-        <v>372800</v>
+        <v>382100</v>
       </c>
       <c r="F44" s="3">
-        <v>393400</v>
+        <v>403200</v>
       </c>
       <c r="G44" s="3">
-        <v>407400</v>
+        <v>417600</v>
       </c>
       <c r="H44" s="3">
-        <v>392300</v>
+        <v>402100</v>
       </c>
       <c r="I44" s="3">
-        <v>348000</v>
+        <v>356600</v>
       </c>
       <c r="J44" s="3">
-        <v>371800</v>
+        <v>381000</v>
       </c>
       <c r="K44" s="3">
         <v>352500</v>
@@ -3433,19 +3433,19 @@
         <v>8</v>
       </c>
       <c r="E45" s="3">
-        <v>1368200</v>
+        <v>1402200</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="3">
-        <v>1541100</v>
+        <v>1579400</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I45" s="3">
-        <v>1283900</v>
+        <v>1315800</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
@@ -3513,25 +3513,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>9859200</v>
+        <v>10104600</v>
       </c>
       <c r="E46" s="3">
-        <v>11758000</v>
+        <v>12050700</v>
       </c>
       <c r="F46" s="3">
-        <v>11319300</v>
+        <v>11601000</v>
       </c>
       <c r="G46" s="3">
-        <v>10334700</v>
+        <v>10592000</v>
       </c>
       <c r="H46" s="3">
-        <v>10221300</v>
+        <v>10475700</v>
       </c>
       <c r="I46" s="3">
-        <v>11057700</v>
+        <v>11333000</v>
       </c>
       <c r="J46" s="3">
-        <v>11550500</v>
+        <v>11838000</v>
       </c>
       <c r="K46" s="3">
         <v>10061700</v>
@@ -3596,25 +3596,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4386600</v>
+        <v>4495700</v>
       </c>
       <c r="E47" s="3">
-        <v>1420000</v>
+        <v>1455400</v>
       </c>
       <c r="F47" s="3">
-        <v>4506500</v>
+        <v>4618700</v>
       </c>
       <c r="G47" s="3">
-        <v>1815600</v>
+        <v>1860800</v>
       </c>
       <c r="H47" s="3">
-        <v>5122500</v>
+        <v>5250000</v>
       </c>
       <c r="I47" s="3">
-        <v>1546500</v>
+        <v>1585000</v>
       </c>
       <c r="J47" s="3">
-        <v>5575300</v>
+        <v>5714100</v>
       </c>
       <c r="K47" s="3">
         <v>1270900</v>
@@ -3679,25 +3679,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>21789100</v>
+        <v>22331400</v>
       </c>
       <c r="E48" s="3">
-        <v>21837700</v>
+        <v>22381300</v>
       </c>
       <c r="F48" s="3">
-        <v>21293000</v>
+        <v>21823000</v>
       </c>
       <c r="G48" s="3">
-        <v>21419500</v>
+        <v>21952600</v>
       </c>
       <c r="H48" s="3">
-        <v>21223900</v>
+        <v>21752200</v>
       </c>
       <c r="I48" s="3">
-        <v>21168800</v>
+        <v>21695700</v>
       </c>
       <c r="J48" s="3">
-        <v>21115800</v>
+        <v>21641400</v>
       </c>
       <c r="K48" s="3">
         <v>21245200</v>
@@ -3762,25 +3762,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>28231100</v>
+        <v>28933800</v>
       </c>
       <c r="E49" s="3">
-        <v>28413800</v>
+        <v>29121000</v>
       </c>
       <c r="F49" s="3">
-        <v>28561800</v>
+        <v>29272800</v>
       </c>
       <c r="G49" s="3">
-        <v>28833100</v>
+        <v>29550800</v>
       </c>
       <c r="H49" s="3">
-        <v>28816900</v>
+        <v>29534200</v>
       </c>
       <c r="I49" s="3">
-        <v>28927100</v>
+        <v>29647100</v>
       </c>
       <c r="J49" s="3">
-        <v>29102200</v>
+        <v>29826600</v>
       </c>
       <c r="K49" s="3">
         <v>29278600</v>
@@ -4011,25 +4011,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>756500</v>
+        <v>775300</v>
       </c>
       <c r="E52" s="3">
-        <v>3745700</v>
+        <v>3838900</v>
       </c>
       <c r="F52" s="3">
-        <v>854800</v>
+        <v>876100</v>
       </c>
       <c r="G52" s="3">
-        <v>3875400</v>
+        <v>3971900</v>
       </c>
       <c r="H52" s="3">
-        <v>841900</v>
+        <v>862800</v>
       </c>
       <c r="I52" s="3">
-        <v>4332500</v>
+        <v>4440400</v>
       </c>
       <c r="J52" s="3">
-        <v>855900</v>
+        <v>877200</v>
       </c>
       <c r="K52" s="3">
         <v>10577400</v>
@@ -4177,25 +4177,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>65022500</v>
+        <v>66641000</v>
       </c>
       <c r="E54" s="3">
-        <v>67175200</v>
+        <v>68847300</v>
       </c>
       <c r="F54" s="3">
-        <v>66535500</v>
+        <v>68191600</v>
       </c>
       <c r="G54" s="3">
-        <v>66278300</v>
+        <v>67928000</v>
       </c>
       <c r="H54" s="3">
-        <v>66226400</v>
+        <v>67874800</v>
       </c>
       <c r="I54" s="3">
-        <v>67032600</v>
+        <v>68701100</v>
       </c>
       <c r="J54" s="3">
-        <v>68199700</v>
+        <v>69897300</v>
       </c>
       <c r="K54" s="3">
         <v>72433700</v>
@@ -4322,25 +4322,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9783600</v>
+        <v>10027100</v>
       </c>
       <c r="E57" s="3">
-        <v>5880100</v>
+        <v>6026500</v>
       </c>
       <c r="F57" s="3">
-        <v>8531000</v>
+        <v>8743400</v>
       </c>
       <c r="G57" s="3">
-        <v>5200300</v>
+        <v>5329800</v>
       </c>
       <c r="H57" s="3">
-        <v>8666100</v>
+        <v>8881800</v>
       </c>
       <c r="I57" s="3">
-        <v>5722300</v>
+        <v>5864700</v>
       </c>
       <c r="J57" s="3">
-        <v>8203600</v>
+        <v>8407800</v>
       </c>
       <c r="K57" s="3">
         <v>4971500</v>
@@ -4405,25 +4405,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5926600</v>
+        <v>6074100</v>
       </c>
       <c r="E58" s="3">
-        <v>7014800</v>
+        <v>7189400</v>
       </c>
       <c r="F58" s="3">
-        <v>7503300</v>
+        <v>7690100</v>
       </c>
       <c r="G58" s="3">
-        <v>8869300</v>
+        <v>9090100</v>
       </c>
       <c r="H58" s="3">
-        <v>6491800</v>
+        <v>6653400</v>
       </c>
       <c r="I58" s="3">
-        <v>6084300</v>
+        <v>6235800</v>
       </c>
       <c r="J58" s="3">
-        <v>6067000</v>
+        <v>6218100</v>
       </c>
       <c r="K58" s="3">
         <v>4662500</v>
@@ -4488,25 +4488,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>24900</v>
+        <v>25500</v>
       </c>
       <c r="E59" s="3">
-        <v>4417900</v>
+        <v>4527900</v>
       </c>
       <c r="F59" s="3">
-        <v>25900</v>
+        <v>26600</v>
       </c>
       <c r="G59" s="3">
-        <v>3807300</v>
+        <v>3902100</v>
       </c>
       <c r="H59" s="3">
-        <v>46500</v>
+        <v>47600</v>
       </c>
       <c r="I59" s="3">
-        <v>3476600</v>
+        <v>3563100</v>
       </c>
       <c r="J59" s="3">
-        <v>9700</v>
+        <v>10000</v>
       </c>
       <c r="K59" s="3">
         <v>5817000</v>
@@ -4571,25 +4571,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>15735000</v>
+        <v>16126700</v>
       </c>
       <c r="E60" s="3">
-        <v>17312800</v>
+        <v>17743800</v>
       </c>
       <c r="F60" s="3">
-        <v>16060300</v>
+        <v>16460000</v>
       </c>
       <c r="G60" s="3">
-        <v>17876900</v>
+        <v>18321900</v>
       </c>
       <c r="H60" s="3">
-        <v>15204400</v>
+        <v>15582800</v>
       </c>
       <c r="I60" s="3">
-        <v>15283300</v>
+        <v>15663700</v>
       </c>
       <c r="J60" s="3">
-        <v>14280400</v>
+        <v>14635800</v>
       </c>
       <c r="K60" s="3">
         <v>15451000</v>
@@ -4654,25 +4654,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>28045200</v>
+        <v>28743300</v>
       </c>
       <c r="E61" s="3">
-        <v>27678900</v>
+        <v>28367900</v>
       </c>
       <c r="F61" s="3">
-        <v>28062500</v>
+        <v>28761000</v>
       </c>
       <c r="G61" s="3">
-        <v>25109000</v>
+        <v>25734000</v>
       </c>
       <c r="H61" s="3">
-        <v>27948000</v>
+        <v>28643600</v>
       </c>
       <c r="I61" s="3">
-        <v>28162000</v>
+        <v>28862900</v>
       </c>
       <c r="J61" s="3">
-        <v>29725700</v>
+        <v>30465600</v>
       </c>
       <c r="K61" s="3">
         <v>28256900</v>
@@ -4737,25 +4737,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2862800</v>
+        <v>2934000</v>
       </c>
       <c r="E62" s="3">
-        <v>3257200</v>
+        <v>3338300</v>
       </c>
       <c r="F62" s="3">
-        <v>3174000</v>
+        <v>3253000</v>
       </c>
       <c r="G62" s="3">
-        <v>3554400</v>
+        <v>3642900</v>
       </c>
       <c r="H62" s="3">
-        <v>3438800</v>
+        <v>3524400</v>
       </c>
       <c r="I62" s="3">
-        <v>3351300</v>
+        <v>3434700</v>
       </c>
       <c r="J62" s="3">
-        <v>3497100</v>
+        <v>3584200</v>
       </c>
       <c r="K62" s="3">
         <v>4216400</v>
@@ -5069,25 +5069,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>50760500</v>
+        <v>52024000</v>
       </c>
       <c r="E66" s="3">
-        <v>52428000</v>
+        <v>53733000</v>
       </c>
       <c r="F66" s="3">
-        <v>51414300</v>
+        <v>52694100</v>
       </c>
       <c r="G66" s="3">
-        <v>50685900</v>
+        <v>51947500</v>
       </c>
       <c r="H66" s="3">
-        <v>50596200</v>
+        <v>51855600</v>
       </c>
       <c r="I66" s="3">
-        <v>50756200</v>
+        <v>52019500</v>
       </c>
       <c r="J66" s="3">
-        <v>51491000</v>
+        <v>52772700</v>
       </c>
       <c r="K66" s="3">
         <v>53294000</v>
@@ -5515,25 +5515,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3444200</v>
+        <v>3529900</v>
       </c>
       <c r="E72" s="3">
-        <v>3880800</v>
+        <v>3977400</v>
       </c>
       <c r="F72" s="3">
-        <v>4227700</v>
+        <v>4332900</v>
       </c>
       <c r="G72" s="3">
-        <v>4547600</v>
+        <v>4660800</v>
       </c>
       <c r="H72" s="3">
-        <v>2992500</v>
+        <v>3066900</v>
       </c>
       <c r="I72" s="3">
-        <v>3742500</v>
+        <v>3835600</v>
       </c>
       <c r="J72" s="3">
-        <v>3940200</v>
+        <v>4038300</v>
       </c>
       <c r="K72" s="3">
         <v>6418700</v>
@@ -5847,25 +5847,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>14262000</v>
+        <v>14617000</v>
       </c>
       <c r="E76" s="3">
-        <v>14747200</v>
+        <v>15114300</v>
       </c>
       <c r="F76" s="3">
-        <v>15121200</v>
+        <v>15497500</v>
       </c>
       <c r="G76" s="3">
-        <v>15592300</v>
+        <v>15980500</v>
       </c>
       <c r="H76" s="3">
-        <v>15630200</v>
+        <v>16019200</v>
       </c>
       <c r="I76" s="3">
-        <v>16276400</v>
+        <v>16681600</v>
       </c>
       <c r="J76" s="3">
-        <v>16708700</v>
+        <v>17124600</v>
       </c>
       <c r="K76" s="3">
         <v>19139700</v>
@@ -6101,25 +6101,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-432300</v>
+        <v>-443000</v>
       </c>
       <c r="E81" s="3">
-        <v>-678700</v>
+        <v>-695600</v>
       </c>
       <c r="F81" s="3">
-        <v>-336100</v>
+        <v>-344500</v>
       </c>
       <c r="G81" s="3">
-        <v>-878600</v>
+        <v>-900500</v>
       </c>
       <c r="H81" s="3">
-        <v>-744600</v>
+        <v>-763100</v>
       </c>
       <c r="I81" s="3">
-        <v>-2639100</v>
+        <v>-2704800</v>
       </c>
       <c r="J81" s="3">
-        <v>-2426200</v>
+        <v>-2486600</v>
       </c>
       <c r="K81" s="3">
         <v>-525600</v>
@@ -6215,25 +6215,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1301200</v>
+        <v>1333600</v>
       </c>
       <c r="E83" s="3">
-        <v>2630400</v>
+        <v>2695900</v>
       </c>
       <c r="F83" s="3">
-        <v>1312000</v>
+        <v>1344600</v>
       </c>
       <c r="G83" s="3">
-        <v>2625000</v>
+        <v>2690400</v>
       </c>
       <c r="H83" s="3">
-        <v>1297900</v>
+        <v>1330200</v>
       </c>
       <c r="I83" s="3">
-        <v>2682300</v>
+        <v>2749100</v>
       </c>
       <c r="J83" s="3">
-        <v>1345500</v>
+        <v>1379000</v>
       </c>
       <c r="K83" s="3">
         <v>2497200</v>
@@ -6713,25 +6713,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>416100</v>
+        <v>426400</v>
       </c>
       <c r="E89" s="3">
-        <v>2389400</v>
+        <v>2448900</v>
       </c>
       <c r="F89" s="3">
-        <v>866700</v>
+        <v>888300</v>
       </c>
       <c r="G89" s="3">
-        <v>1872900</v>
+        <v>1919500</v>
       </c>
       <c r="H89" s="3">
-        <v>919700</v>
+        <v>942600</v>
       </c>
       <c r="I89" s="3">
-        <v>2595800</v>
+        <v>2660500</v>
       </c>
       <c r="J89" s="3">
-        <v>1093700</v>
+        <v>1120900</v>
       </c>
       <c r="K89" s="3">
         <v>2712600</v>
@@ -7076,25 +7076,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-705700</v>
+        <v>-723300</v>
       </c>
       <c r="E94" s="3">
-        <v>-2161400</v>
+        <v>-2215200</v>
       </c>
       <c r="F94" s="3">
-        <v>-952100</v>
+        <v>-975800</v>
       </c>
       <c r="G94" s="3">
-        <v>-2322400</v>
+        <v>-2380200</v>
       </c>
       <c r="H94" s="3">
-        <v>-1248200</v>
+        <v>-1279300</v>
       </c>
       <c r="I94" s="3">
-        <v>-2497500</v>
+        <v>-2559700</v>
       </c>
       <c r="J94" s="3">
-        <v>-1657800</v>
+        <v>-1699100</v>
       </c>
       <c r="K94" s="3">
         <v>-3290400</v>
@@ -7190,25 +7190,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-114100</v>
+      </c>
+      <c r="F96" s="3">
+        <v>-86400</v>
+      </c>
+      <c r="G96" s="3">
+        <v>-95300</v>
+      </c>
+      <c r="H96" s="3">
         <v>-42100</v>
       </c>
-      <c r="E96" s="3">
-        <v>-111300</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-84300</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-92900</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-41100</v>
-      </c>
       <c r="I96" s="3">
-        <v>-33500</v>
+        <v>-34300</v>
       </c>
       <c r="J96" s="3">
-        <v>-17300</v>
+        <v>-17700</v>
       </c>
       <c r="K96" s="3">
         <v>-40300</v>
@@ -7522,25 +7522,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1464300</v>
+        <v>-1500800</v>
       </c>
       <c r="E100" s="3">
-        <v>357700</v>
+        <v>366600</v>
       </c>
       <c r="F100" s="3">
-        <v>1066700</v>
+        <v>1093200</v>
       </c>
       <c r="G100" s="3">
-        <v>-850500</v>
+        <v>-871700</v>
       </c>
       <c r="H100" s="3">
-        <v>-644100</v>
+        <v>-660100</v>
       </c>
       <c r="I100" s="3">
-        <v>1190900</v>
+        <v>1220600</v>
       </c>
       <c r="J100" s="3">
-        <v>1779900</v>
+        <v>1824200</v>
       </c>
       <c r="K100" s="3">
         <v>-4320800</v>
@@ -7605,25 +7605,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="E101" s="3">
-        <v>-16200</v>
+        <v>-16600</v>
       </c>
       <c r="F101" s="3">
-        <v>-5400</v>
+        <v>-5500</v>
       </c>
       <c r="G101" s="3">
-        <v>35700</v>
+        <v>36600</v>
       </c>
       <c r="H101" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="I101" s="3">
-        <v>-22700</v>
+        <v>-23300</v>
       </c>
       <c r="J101" s="3">
-        <v>11900</v>
+        <v>12200</v>
       </c>
       <c r="K101" s="3">
         <v>-20700</v>
@@ -7688,25 +7688,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1758300</v>
+        <v>-1802100</v>
       </c>
       <c r="E102" s="3">
-        <v>569500</v>
+        <v>583700</v>
       </c>
       <c r="F102" s="3">
-        <v>975900</v>
+        <v>1000200</v>
       </c>
       <c r="G102" s="3">
-        <v>-1264400</v>
+        <v>-1295900</v>
       </c>
       <c r="H102" s="3">
-        <v>-968300</v>
+        <v>-992400</v>
       </c>
       <c r="I102" s="3">
-        <v>1266600</v>
+        <v>1298100</v>
       </c>
       <c r="J102" s="3">
-        <v>1227700</v>
+        <v>1258200</v>
       </c>
       <c r="K102" s="3">
         <v>-4919300</v>

--- a/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>TIIAY</t>
   </si>
@@ -656,378 +656,404 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>4352900</v>
-      </c>
-      <c r="E8" s="3">
-        <v>9359200</v>
-      </c>
-      <c r="F8" s="3">
-        <v>4548900</v>
-      </c>
-      <c r="G8" s="3">
-        <v>8690200</v>
-      </c>
-      <c r="H8" s="3">
-        <v>4260900</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>9116700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4399400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>8222800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3965000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>8400700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4089000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>8123100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3969600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>8025100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4045700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>8464400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>4324400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>10483300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>5425500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>10580500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>5348200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>11236400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>5134800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>10333300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>5144100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>11041500</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>1798700</v>
-      </c>
-      <c r="E9" s="3">
-        <v>4061600</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1881800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>3568700</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1740000</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>3961900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1834200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3323100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1589700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3510300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1619700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3007800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1478000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3054000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1499800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2782900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1388700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3552400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1755400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>3517400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1818200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1594500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1979300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>6005000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1977500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1573400</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>2554100</v>
-      </c>
-      <c r="E10" s="3">
-        <v>5297700</v>
-      </c>
-      <c r="F10" s="3">
-        <v>2667100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>5121500</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2520900</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>5154800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2565200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4899700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2375300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>4890400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2469300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>5115300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2491600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>4971000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2546000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>5681500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2935600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>6930900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>3670100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>7063100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>3530000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>9641800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>3155600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>4328300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>3166600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>9468100</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,8 +1083,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,8 +1168,14 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,174 +1257,192 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>97500</v>
-      </c>
-      <c r="E14" s="3">
-        <v>226000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>155100</v>
-      </c>
-      <c r="G14" s="3">
-        <v>476300</v>
-      </c>
-      <c r="H14" s="3">
-        <v>465200</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>74200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>334500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>317700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>77300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>4467600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>60300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>482500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>424300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>155600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>43600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>111300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>26200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>440100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>39200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>-408200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>23900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>3320400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>2228500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>166900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>800400</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>1333600</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2695900</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1344600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2690400</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1330200</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="3">
         <v>2749100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>1379000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>2497200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>1204500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>2408900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>1230900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>2442400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1195500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>2262100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>1177000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>2561500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>1310200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>2838000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>1545900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>2936300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>1512000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>2523100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>1157400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>2330000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>1158400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>2442000</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1469,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>4123600</v>
-      </c>
-      <c r="E17" s="3">
-        <v>8698000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>4184500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>8425500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4440400</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>8885200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4354000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>7790800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3737600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>12769600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3597900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7601800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3922000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>6965800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3438600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>7327600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3742900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>8979700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4414900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>8360700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4531200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>12517400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>6272300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>8561100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>4329400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>9482300</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>229300</v>
-      </c>
-      <c r="E18" s="3">
-        <v>661200</v>
-      </c>
-      <c r="F18" s="3">
-        <v>364400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>264700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-179400</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>231500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>45400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>432000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>227400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-4368900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>491100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>521200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>47600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1059200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>607200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1136700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>581500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1503600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1010600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>2219900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>817000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1281100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-1137500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1772200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>814700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>1559200</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,423 +1680,455 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-561600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-808500</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-546000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-620300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-415400</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>170600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-240300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-29400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-327500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>173500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-290800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>42000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-293100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>44900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-307200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>532400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>152700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-2300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-448300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-24700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-462900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>4700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-364400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-59300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-383200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-36200</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>1001300</v>
-      </c>
-      <c r="E21" s="3">
-        <v>2548600</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1163000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>2334800</v>
-      </c>
-      <c r="H21" s="3">
-        <v>735400</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>3151100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1184000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2899800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1104400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1786600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1432300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>3005600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>950100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>3366200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1476900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>4230500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>2044400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>4339300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>2108200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>5131500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1866100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1246800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-344500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>4042800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1589900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>3964900</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3">
-        <v>240300</v>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="3">
-        <v>231500</v>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>767600</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>683300</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>648300</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3">
         <v>632100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
         <v>597400</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U22" s="3">
         <v>699300</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3">
         <v>792700</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="3">
         <v>863500</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3">
         <v>747600</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC22" s="3">
         <v>720300</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE22" s="3">
         <v>791700</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-332300</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-387700</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-181600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-587000</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-594800</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>-365500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-194900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-280700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-100100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-4843800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>200300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-68900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-245500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>506700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>300000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>969800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>734200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>708600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>562300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1331700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>354100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2023900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1501900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>992600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>431500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>731300</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>46500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>93000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>69800</v>
-      </c>
-      <c r="G24" s="3">
-        <v>158400</v>
-      </c>
-      <c r="H24" s="3">
-        <v>94100</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>2175300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2223000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>111000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>54400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>4213900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-38800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-7500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-6105100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-240800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>181100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>89500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>141300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>129800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>461100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>130400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>82800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-56500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>326100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>171300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>36200</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2210,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-378800</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-480700</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-251400</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-745400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-688900</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2540800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2417900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-391700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-154500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-9057700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>239100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-61400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-205300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>6611800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>540700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>788700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>644700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>567400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>432400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>870500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>223700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2106700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1445400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>666500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>260200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-443000</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-695600</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-344500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-900500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-763100</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2704800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2486600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-525600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-222000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-9231100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>149700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-160500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-228500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>6529000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>519000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>739600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>610900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>407400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>368700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>648200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>197400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2324400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>584100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>220700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,31 +2477,37 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2405,27 +2527,27 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>18700</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
@@ -2444,8 +2566,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2655,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,174 +2744,192 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>561600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>808500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>546000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>620300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>415400</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-170600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>240300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>29400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>327500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-173500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>290800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-42000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>293100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-44900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>307200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-532400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-152700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>2300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>448300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>24700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>462900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>364400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>59300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>383200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>36200</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-443000</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-695600</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-344500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-900500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-763100</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2704800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2486600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-525600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-222000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-9231100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>149700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-160500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-228500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>6529000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>519000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>739600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>610900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>426100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>368700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>648200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>197400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2324400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>584100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>220700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +3011,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-443000</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-695600</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-344500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-900500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-763100</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2704800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2486600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-525600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-222000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-9231100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>149700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-160500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-228500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>6529000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>519000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>739600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>610900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>426100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>368700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>648200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>197400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2324400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>584100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>220700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3231,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,340 +3264,366 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1423300</v>
+        <v>2413600</v>
       </c>
       <c r="E41" s="3">
-        <v>3225300</v>
+        <v>595700</v>
       </c>
       <c r="F41" s="3">
-        <v>3645100</v>
+        <v>1386300</v>
       </c>
       <c r="G41" s="3">
-        <v>2641600</v>
+        <v>3218700</v>
       </c>
       <c r="H41" s="3">
-        <v>2946200</v>
+        <v>3483300</v>
       </c>
       <c r="I41" s="3">
+        <v>2603700</v>
+      </c>
+      <c r="J41" s="3">
+        <v>2890000</v>
+      </c>
+      <c r="K41" s="3">
         <v>3937500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3897600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2601600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3560300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>7484600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4784700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>5351100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4623500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4816400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2966300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3930500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3561800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3663300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2630100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1999900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2515600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2267600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2816600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2308000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1844600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>3925400</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2241800</v>
+        <v>2094600</v>
       </c>
       <c r="E42" s="3">
-        <v>2847600</v>
+        <v>2237200</v>
       </c>
       <c r="F42" s="3">
-        <v>2018000</v>
+        <v>1929000</v>
       </c>
       <c r="G42" s="3">
-        <v>2101100</v>
+        <v>2272600</v>
       </c>
       <c r="H42" s="3">
-        <v>1859700</v>
+        <v>1928500</v>
       </c>
       <c r="I42" s="3">
+        <v>2036000</v>
+      </c>
+      <c r="J42" s="3">
+        <v>1824200</v>
+      </c>
+      <c r="K42" s="3">
         <v>1772200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>2112200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>2048900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2308900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>2592100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1643300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1573400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>3134900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>1250700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>1293200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>1098500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>1074500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>1166200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>1527600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1307000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>1882800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1651300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>1694600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1564700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>1831500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>1570100</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6009800</v>
+        <v>5261000</v>
       </c>
       <c r="E43" s="3">
-        <v>4193400</v>
+        <v>3594800</v>
       </c>
       <c r="F43" s="3">
-        <v>5534700</v>
+        <v>6108500</v>
       </c>
       <c r="G43" s="3">
-        <v>3852200</v>
+        <v>4708700</v>
       </c>
       <c r="H43" s="3">
-        <v>5267700</v>
+        <v>5289000</v>
       </c>
       <c r="I43" s="3">
+        <v>3777300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>5167300</v>
+      </c>
+      <c r="K43" s="3">
         <v>3950800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5447200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3698500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4971500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3694600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4720100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3787500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4649900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3621600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>4836600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>4119300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>5433800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>4973200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>6253600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>4826800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>6313500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>4907900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>5703000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>4508400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>5900700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>4597300</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>429700</v>
+        <v>350200</v>
       </c>
       <c r="E44" s="3">
-        <v>382100</v>
+        <v>331100</v>
       </c>
       <c r="F44" s="3">
-        <v>403200</v>
+        <v>418600</v>
       </c>
       <c r="G44" s="3">
-        <v>417600</v>
+        <v>381300</v>
       </c>
       <c r="H44" s="3">
-        <v>402100</v>
+        <v>385300</v>
       </c>
       <c r="I44" s="3">
+        <v>411600</v>
+      </c>
+      <c r="J44" s="3">
+        <v>394400</v>
+      </c>
+      <c r="K44" s="3">
         <v>356600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>381000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>352500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>336200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>305700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>385500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>366100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>350200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>286300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>282300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>279300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>307600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>303500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>366300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>371700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>388800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>460100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>344500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>352500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>357900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>318400</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3433,414 +3631,444 @@
         <v>8</v>
       </c>
       <c r="E45" s="3">
-        <v>1402200</v>
+        <v>25672300</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="3">
-        <v>1579400</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
+        <v>1444700</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1100</v>
       </c>
       <c r="I45" s="3">
+        <v>1611400</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>1315800</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>1360100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>1176200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1005800</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S45" s="3">
         <v>853800</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U45" s="3">
         <v>1030900</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W45" s="3">
         <v>938600</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1203500</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="3">
         <v>1038600</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3">
         <v>1109000</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE45" s="3">
         <v>932200</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>10104600</v>
+        <v>10119300</v>
       </c>
       <c r="E46" s="3">
-        <v>12050700</v>
+        <v>32431200</v>
       </c>
       <c r="F46" s="3">
-        <v>11601000</v>
+        <v>9842500</v>
       </c>
       <c r="G46" s="3">
-        <v>10592000</v>
+        <v>12026100</v>
       </c>
       <c r="H46" s="3">
-        <v>10475700</v>
+        <v>11087000</v>
       </c>
       <c r="I46" s="3">
+        <v>10440000</v>
+      </c>
+      <c r="J46" s="3">
+        <v>10276000</v>
+      </c>
+      <c r="K46" s="3">
         <v>11333000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>11838000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10061700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>11177000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>15253300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>11533600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>12083900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>12758400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>10762900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>9378500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>10458600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>10377800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>11044900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>10777500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>9708800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>11100700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>10325500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>10558800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>9842500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>9934700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>11343400</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4495700</v>
+        <v>1502300</v>
       </c>
       <c r="E47" s="3">
-        <v>1455400</v>
+        <v>1340400</v>
       </c>
       <c r="F47" s="3">
-        <v>4618700</v>
+        <v>1891300</v>
       </c>
       <c r="G47" s="3">
-        <v>1860800</v>
+        <v>1923300</v>
       </c>
       <c r="H47" s="3">
-        <v>5250000</v>
+        <v>1857500</v>
       </c>
       <c r="I47" s="3">
+        <v>1994500</v>
+      </c>
+      <c r="J47" s="3">
+        <v>2495700</v>
+      </c>
+      <c r="K47" s="3">
         <v>1585000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>5714100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1270900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>8292400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>4296300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>7922800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>3883300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>7397500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>3628500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>7896300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>4272000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>9769100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>3208000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>6742300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>3669200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>5077900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>2973800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>3953000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>2599000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>4036200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>3033800</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>22331400</v>
+        <v>8917000</v>
       </c>
       <c r="E48" s="3">
-        <v>22381300</v>
+        <v>8012400</v>
       </c>
       <c r="F48" s="3">
-        <v>21823000</v>
+        <v>21752100</v>
       </c>
       <c r="G48" s="3">
-        <v>21952600</v>
+        <v>22335600</v>
       </c>
       <c r="H48" s="3">
-        <v>21752200</v>
+        <v>20854100</v>
       </c>
       <c r="I48" s="3">
+        <v>21637600</v>
+      </c>
+      <c r="J48" s="3">
+        <v>21337500</v>
+      </c>
+      <c r="K48" s="3">
         <v>21695700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>21641400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>21245200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>20531400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>19685100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>19160200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>19327100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>18865200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>18085900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>18349000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>19645100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>20250600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>22770300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>24117600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>23400900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>23709900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>19099100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>17481300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>17492200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>17704200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>18168600</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>28933800</v>
+        <v>19252700</v>
       </c>
       <c r="E49" s="3">
-        <v>29121000</v>
+        <v>18791400</v>
       </c>
       <c r="F49" s="3">
-        <v>29272800</v>
+        <v>28183200</v>
       </c>
       <c r="G49" s="3">
-        <v>29550800</v>
+        <v>29061600</v>
       </c>
       <c r="H49" s="3">
-        <v>29534200</v>
+        <v>27973100</v>
       </c>
       <c r="I49" s="3">
+        <v>29126600</v>
+      </c>
+      <c r="J49" s="3">
+        <v>28971100</v>
+      </c>
+      <c r="K49" s="3">
         <v>29647100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>29826600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>29278600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>28359200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>27877600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>31416400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>31655500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>30996200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>29510100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>30568200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>32440400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>32756800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>35897900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>42218100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>40927000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>41849100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>42179800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>37227500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>39297400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>39766300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>40246100</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4150,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,91 +4239,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>775300</v>
+        <v>1777800</v>
       </c>
       <c r="E52" s="3">
-        <v>3838900</v>
+        <v>2852200</v>
       </c>
       <c r="F52" s="3">
-        <v>876100</v>
+        <v>2368100</v>
       </c>
       <c r="G52" s="3">
-        <v>3971900</v>
+        <v>475300</v>
       </c>
       <c r="H52" s="3">
-        <v>862800</v>
+        <v>2436500</v>
       </c>
       <c r="I52" s="3">
+        <v>792600</v>
+      </c>
+      <c r="J52" s="3">
+        <v>2602100</v>
+      </c>
+      <c r="K52" s="3">
         <v>4440400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>877200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>10577400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3775700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>7893300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>8560300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>12529700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>7984700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>11035200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1120900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>5791600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1022200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>8919000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1248300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>3597400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1498800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>3106300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1190700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2232200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>991500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2731800</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4417,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>66641000</v>
+        <v>42229500</v>
       </c>
       <c r="E54" s="3">
-        <v>68847300</v>
+        <v>65424800</v>
       </c>
       <c r="F54" s="3">
-        <v>68191600</v>
+        <v>64912100</v>
       </c>
       <c r="G54" s="3">
-        <v>67928000</v>
+        <v>68706800</v>
       </c>
       <c r="H54" s="3">
-        <v>67874800</v>
+        <v>65164100</v>
       </c>
       <c r="I54" s="3">
+        <v>66953100</v>
+      </c>
+      <c r="J54" s="3">
+        <v>66580800</v>
+      </c>
+      <c r="K54" s="3">
         <v>68701100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>69897300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>72433700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>72135600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>75005600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>78593200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>79479500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>78002100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>73022600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>67313000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>72607700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>74176400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>81840100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>85103700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>81303400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>83236400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>77620700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>70411200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>71463300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>72432900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>75523700</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4543,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,506 +4576,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10027100</v>
+        <v>7694600</v>
       </c>
       <c r="E57" s="3">
-        <v>6026500</v>
+        <v>3896900</v>
       </c>
       <c r="F57" s="3">
-        <v>8743400</v>
+        <v>9767000</v>
       </c>
       <c r="G57" s="3">
-        <v>5329800</v>
+        <v>6014100</v>
       </c>
       <c r="H57" s="3">
-        <v>8881800</v>
+        <v>8355200</v>
       </c>
       <c r="I57" s="3">
+        <v>5253300</v>
+      </c>
+      <c r="J57" s="3">
+        <v>8712500</v>
+      </c>
+      <c r="K57" s="3">
         <v>5864700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>8407800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4971500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>10505600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5595000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>8740100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4093300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>7438800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>4122300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>6131900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3279300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>7170600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>5046700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>7912200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>4031500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>8182000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>5287600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>6761900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>3978100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>7476300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>5100200</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6074100</v>
+        <v>4255000</v>
       </c>
       <c r="E58" s="3">
-        <v>7189400</v>
+        <v>14453000</v>
       </c>
       <c r="F58" s="3">
-        <v>7690100</v>
+        <v>5916500</v>
       </c>
       <c r="G58" s="3">
-        <v>9090100</v>
+        <v>7305200</v>
       </c>
       <c r="H58" s="3">
-        <v>6653400</v>
+        <v>7348600</v>
       </c>
       <c r="I58" s="3">
+        <v>9137600</v>
+      </c>
+      <c r="J58" s="3">
+        <v>6526500</v>
+      </c>
+      <c r="K58" s="3">
         <v>6235800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>6218100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>4662500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4146700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>7044500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>5442700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>5541700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>6075000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>4233000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>4583400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>4700700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>4584000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>4388300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>5239300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>4011500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>6679600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>6594700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>7155100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>6297000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>5512000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>5139700</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>25500</v>
+        <v>23400</v>
       </c>
       <c r="E59" s="3">
-        <v>4527900</v>
+        <v>11864400</v>
       </c>
       <c r="F59" s="3">
-        <v>26600</v>
+        <v>24800</v>
       </c>
       <c r="G59" s="3">
-        <v>3902100</v>
+        <v>2823000</v>
       </c>
       <c r="H59" s="3">
+        <v>26500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1748900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>46700</v>
+      </c>
+      <c r="K59" s="3">
+        <v>3563100</v>
+      </c>
+      <c r="L59" s="3">
+        <v>10000</v>
+      </c>
+      <c r="M59" s="3">
+        <v>5817000</v>
+      </c>
+      <c r="N59" s="3">
+        <v>297100</v>
+      </c>
+      <c r="O59" s="3">
+        <v>5100700</v>
+      </c>
+      <c r="P59" s="3">
+        <v>261700</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>3603300</v>
+      </c>
+      <c r="R59" s="3">
+        <v>269800</v>
+      </c>
+      <c r="S59" s="3">
+        <v>2761800</v>
+      </c>
+      <c r="T59" s="3">
+        <v>58100</v>
+      </c>
+      <c r="U59" s="3">
+        <v>3511600</v>
+      </c>
+      <c r="V59" s="3">
+        <v>46900</v>
+      </c>
+      <c r="W59" s="3">
+        <v>3550100</v>
+      </c>
+      <c r="X59" s="3">
+        <v>51400</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>3972700</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>77800</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>3354700</v>
+      </c>
+      <c r="AB59" s="3">
         <v>47600</v>
       </c>
-      <c r="I59" s="3">
-        <v>3563100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>10000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>5817000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>297100</v>
-      </c>
-      <c r="M59" s="3">
-        <v>5100700</v>
-      </c>
-      <c r="N59" s="3">
-        <v>261700</v>
-      </c>
-      <c r="O59" s="3">
-        <v>3603300</v>
-      </c>
-      <c r="P59" s="3">
-        <v>269800</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>2761800</v>
-      </c>
-      <c r="R59" s="3">
-        <v>58100</v>
-      </c>
-      <c r="S59" s="3">
-        <v>3511600</v>
-      </c>
-      <c r="T59" s="3">
-        <v>46900</v>
-      </c>
-      <c r="U59" s="3">
-        <v>3550100</v>
-      </c>
-      <c r="V59" s="3">
-        <v>51400</v>
-      </c>
-      <c r="W59" s="3">
-        <v>3972700</v>
-      </c>
-      <c r="X59" s="3">
-        <v>77800</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>3354700</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>47600</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>3631100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>81300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>3362100</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>16126700</v>
+        <v>11973000</v>
       </c>
       <c r="E60" s="3">
-        <v>17743800</v>
+        <v>32086100</v>
       </c>
       <c r="F60" s="3">
-        <v>16460000</v>
+        <v>15708300</v>
       </c>
       <c r="G60" s="3">
-        <v>18321900</v>
+        <v>17707500</v>
       </c>
       <c r="H60" s="3">
-        <v>15582800</v>
+        <v>15730300</v>
       </c>
       <c r="I60" s="3">
+        <v>18059000</v>
+      </c>
+      <c r="J60" s="3">
+        <v>15285700</v>
+      </c>
+      <c r="K60" s="3">
         <v>15663700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>14635800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>15451000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>14949400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>17740200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>14444500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>13238300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>13783600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>11117000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>10773400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>11491600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>11801500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>12985100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>13202900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>12015700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>14939300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>15236900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>13964600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>13906200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>13069500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>13602000</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>28743300</v>
+        <v>13305800</v>
       </c>
       <c r="E61" s="3">
-        <v>28367900</v>
+        <v>14091900</v>
       </c>
       <c r="F61" s="3">
-        <v>28761000</v>
+        <v>27997600</v>
       </c>
       <c r="G61" s="3">
-        <v>25734000</v>
+        <v>28768700</v>
       </c>
       <c r="H61" s="3">
-        <v>28643600</v>
+        <v>27484100</v>
       </c>
       <c r="I61" s="3">
+        <v>25672500</v>
+      </c>
+      <c r="J61" s="3">
+        <v>28097600</v>
+      </c>
+      <c r="K61" s="3">
         <v>28862900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>30465600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>28256900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>28920600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>28346000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>27642900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>26142800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>26892200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>25944400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>28929400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>29868000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>32482900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>33295700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>37070600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>33809700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>35096500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>27956700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>27723200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>25709700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>28833500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>28755500</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2934000</v>
+        <v>1361800</v>
       </c>
       <c r="E62" s="3">
-        <v>3338300</v>
+        <v>1010400</v>
       </c>
       <c r="F62" s="3">
-        <v>3253000</v>
+        <v>2198700</v>
       </c>
       <c r="G62" s="3">
-        <v>3642900</v>
+        <v>1434700</v>
       </c>
       <c r="H62" s="3">
-        <v>3524400</v>
+        <v>2012100</v>
       </c>
       <c r="I62" s="3">
+        <v>1303500</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2221900</v>
+      </c>
+      <c r="K62" s="3">
         <v>3434700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3584200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4216400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3527600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>5027000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3509600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>7147400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>5774600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>7196200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>5323400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>7909100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>5880000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>9145500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>7214000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>9204200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>7100600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>8702600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>4465800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>6158700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>4571000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>7052500</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5195,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5284,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5373,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>52024000</v>
+        <v>26950700</v>
       </c>
       <c r="E66" s="3">
-        <v>53733000</v>
+        <v>47760600</v>
       </c>
       <c r="F66" s="3">
-        <v>52694100</v>
+        <v>46563800</v>
       </c>
       <c r="G66" s="3">
-        <v>51947500</v>
+        <v>49349000</v>
       </c>
       <c r="H66" s="3">
-        <v>51855600</v>
+        <v>46322000</v>
       </c>
       <c r="I66" s="3">
+        <v>47014200</v>
+      </c>
+      <c r="J66" s="3">
+        <v>46840500</v>
+      </c>
+      <c r="K66" s="3">
         <v>52019500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>52772700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>53294000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>52782600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>56127100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>50548600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>51473700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>51146900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>46875800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>46319400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>50701100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>51678600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>58165000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>60332000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>57835400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>59776500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>54521000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>48500700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>48032000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>48898300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>51854100</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5499,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5584,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5673,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5762,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5851,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>3529900</v>
-      </c>
-      <c r="E72" s="3">
-        <v>3977400</v>
-      </c>
-      <c r="F72" s="3">
-        <v>4332900</v>
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G72" s="3">
-        <v>4660800</v>
-      </c>
-      <c r="H72" s="3">
-        <v>3066900</v>
-      </c>
-      <c r="I72" s="3">
+        <v>-1592800</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" s="3">
         <v>3835600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4038300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>6418700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>6722300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>6912200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>16264400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>16093200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>15713400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>15440700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>9793600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>9747300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>9963300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>9994200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>10410000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>9644100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>9345900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>9238400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>9251800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>10729700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>10540800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>10403600</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +6029,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +6118,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6207,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>14617000</v>
+        <v>13659400</v>
       </c>
       <c r="E76" s="3">
-        <v>15114300</v>
+        <v>13652600</v>
       </c>
       <c r="F76" s="3">
-        <v>15497500</v>
+        <v>14237800</v>
       </c>
       <c r="G76" s="3">
-        <v>15980500</v>
+        <v>15083500</v>
       </c>
       <c r="H76" s="3">
-        <v>16019200</v>
+        <v>14809500</v>
       </c>
       <c r="I76" s="3">
+        <v>15751100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>15713800</v>
+      </c>
+      <c r="K76" s="3">
         <v>16681600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>17124600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>19139700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>19352900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>18878500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>28044600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>28005900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>26855200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>26146800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>20993600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>21906600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>22497800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>23675100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>24771700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>23468000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>23459900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>23099700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>21910500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>23431300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>23534500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>23669600</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6385,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-443000</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-695600</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-344500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-900500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-763100</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2704800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2486600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-525600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-222000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-9231100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>149700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-160500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-228500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>6529000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>519000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>739600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>610900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>426100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>368700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>648200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>197400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2324400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>584100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>220700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,91 +6605,99 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>1333600</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2695900</v>
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F83" s="3">
-        <v>1344600</v>
+        <v>1304900</v>
       </c>
       <c r="G83" s="3">
-        <v>2690400</v>
+        <v>1322000</v>
       </c>
       <c r="H83" s="3">
-        <v>1330200</v>
+        <v>1220800</v>
       </c>
       <c r="I83" s="3">
+        <v>474600</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1229700</v>
+      </c>
+      <c r="K83" s="3">
         <v>2749100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1379000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>2497200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1204500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>2408900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1232000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>2442400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1195500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>2262100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1177000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>2561500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1310200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>2838000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1545900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>2936300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1512000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>2523100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>1157400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>2330000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>1158400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>2442000</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6779,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6868,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6957,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +7046,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +7135,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>426400</v>
-      </c>
-      <c r="E89" s="3">
-        <v>2448900</v>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F89" s="3">
-        <v>888300</v>
+        <v>415400</v>
       </c>
       <c r="G89" s="3">
-        <v>1919500</v>
-      </c>
-      <c r="H89" s="3">
-        <v>942600</v>
-      </c>
-      <c r="I89" s="3">
+        <v>1557400</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3">
+        <v>924600</v>
+      </c>
+      <c r="K89" s="3">
         <v>2660500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1120900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2712600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1169700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2613800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1117800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2073000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1334100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2514400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1574500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>4396400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2585500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>3281600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1699100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>3692700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1776400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>2382400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1032300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>2830600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1021100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>2482600</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,91 +7261,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-1076000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-1207000</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F91" s="3">
-        <v>-789000</v>
+        <v>-1160900</v>
       </c>
       <c r="G91" s="3">
-        <v>-919000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-1054000</v>
-      </c>
-      <c r="I91" s="3">
+        <v>-1334100</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-1145200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1003000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2713000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1438000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1151000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2364000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-872000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1187000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-924700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1275700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-2787800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-90500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1239300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-1778000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-937100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-2501000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-2622500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-674200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-536900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-3041500</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7435,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7524,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-723300</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-2215200</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F94" s="3">
-        <v>-975800</v>
+        <v>-704500</v>
       </c>
       <c r="G94" s="3">
-        <v>-2380200</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-1279300</v>
-      </c>
-      <c r="I94" s="3">
+        <v>-1236900</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1254900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2559700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1699100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-3290400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-822600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3139600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1165200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-2391800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-889800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1457200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-994300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1762900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1220700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1480300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1075500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-2337500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-1498800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-2488800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1073300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-2426600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-1653600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-2909700</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,91 +7650,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-43200</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-114100</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F96" s="3">
-        <v>-86400</v>
+        <v>42100</v>
       </c>
       <c r="G96" s="3">
-        <v>-95300</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-42100</v>
-      </c>
-      <c r="I96" s="3">
+        <v>27600</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
+        <v>41300</v>
+      </c>
+      <c r="K96" s="3">
         <v>-34300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-17700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-40300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-28300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-34700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-19400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-361800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-25400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-33900</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-388400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-43600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-38500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-7300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-289400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-29900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-40200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-18800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-243800</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-18700</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7824,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7913,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,253 +8002,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-1500800</v>
-      </c>
-      <c r="E100" s="3">
-        <v>366600</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F100" s="3">
-        <v>1093200</v>
+        <v>-1461900</v>
       </c>
       <c r="G100" s="3">
-        <v>-871700</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-660100</v>
-      </c>
-      <c r="I100" s="3">
+        <v>-725100</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-647500</v>
+      </c>
+      <c r="K100" s="3">
         <v>1220600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1824200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-4320800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-4462300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2662500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-483500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>762400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-576600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-144600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1498700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-2033500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1206500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-29200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-128600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1281100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>279900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-432900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>548300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-1607500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-1103500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-429300</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="E101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="H101" s="3">
+        <v>10800</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-170400</v>
+      </c>
+      <c r="J101" s="3">
+        <v>160000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="L101" s="3">
+        <v>12200</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="N101" s="3">
+        <v>156700</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-37900</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>51700</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="S101" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="T101" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="U101" s="3">
+        <v>-163600</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-90500</v>
+      </c>
+      <c r="W101" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>5900</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>7200</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-16600</v>
       </c>
-      <c r="F101" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="G101" s="3">
-        <v>36600</v>
-      </c>
-      <c r="H101" s="3">
-        <v>4400</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-23300</v>
-      </c>
-      <c r="J101" s="3">
-        <v>12200</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-20700</v>
-      </c>
-      <c r="L101" s="3">
-        <v>156700</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-37900</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-37700</v>
-      </c>
-      <c r="O101" s="3">
-        <v>51700</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-14800</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-163600</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-90500</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-17500</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="W101" s="3">
-        <v>5900</v>
-      </c>
-      <c r="X101" s="3">
-        <v>7200</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-16600</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-56000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-65900</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1802100</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>583700</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>1000200</v>
+        <v>-1755300</v>
       </c>
       <c r="G102" s="3">
-        <v>-1295900</v>
+        <v>-415600</v>
       </c>
       <c r="H102" s="3">
-        <v>-992400</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-973500</v>
+      </c>
+      <c r="K102" s="3">
         <v>1298100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1258200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-4919300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3958500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>2098800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-568600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>495400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-147100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>903600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-927900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>436400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>67600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1754600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>491200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>80000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>564600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-553600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>490700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-1259400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1756800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-922300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>TIIAY</t>
   </si>
@@ -656,137 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -811,71 +814,74 @@
       <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>9116700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4399400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8222800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3965000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8400700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4089000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8123100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3969600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8025100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4045700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8464400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4324400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10483300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5425500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10580500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5348200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11236400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5134800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10333300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5144100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11041500</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -900,71 +906,74 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>3961900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1834200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3323100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1589700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3510300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1619700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3007800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1478000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3054000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1499800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2782900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1388700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3552400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1755400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3517400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1818200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1594500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1979300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6005000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1977500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1573400</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -989,71 +998,74 @@
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>5154800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2565200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4899700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2375300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4890400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2469300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5115300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2491600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4971000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2546000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5681500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2935600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6930900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3670100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>7063100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3530000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9641800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3155600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4328300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3166600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>9468100</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1085,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1174,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1289,71 +1308,74 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>74200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>334500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>317700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>77300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4467600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>60300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>482500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>424300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>155600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>43600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>111300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>26200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>440100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>39200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-408200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>23900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3320400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2228500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>166900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>800400</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1378,71 +1400,74 @@
       <c r="J15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="3">
         <v>2749100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1379000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2497200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1204500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2408900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1230900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2442400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1195500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2262100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1177000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2561500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1310200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2838000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1545900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2936300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1512000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2523100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1157400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2330000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1158400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2442000</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,8 +1496,9 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1497,71 +1523,74 @@
       <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>8885200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4354000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7790800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3737600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12769600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3597900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7601800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3922000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6965800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3438600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7327600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3742900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8979700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4414900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8360700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4531200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>12517400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6272300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8561100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4329400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9482300</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1586,71 +1615,74 @@
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>231500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>45400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>432000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>227400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4368900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>491100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>521200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>47600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1059200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>607200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1136700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>581500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1503600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1010600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2219900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>817000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1281100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1137500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1772200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>814700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1559200</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1708,71 +1741,74 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>170600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-240300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-29400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-327500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>173500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-290800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>42000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-293100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>44900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-307200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>532400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>152700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-448300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-24700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-462900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-364400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-59300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-383200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-36200</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1797,71 +1833,74 @@
       <c r="J21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3">
         <v>3151100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1184000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2899800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1104400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1786600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1432300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3005600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>950100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3366200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1476900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4230500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2044400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4339300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2108200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5131500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1866100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1246800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-344500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4042800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1589900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3964900</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1886,71 +1925,74 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>767600</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>683300</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3">
         <v>648300</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>632100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3">
         <v>597400</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V22" s="3">
         <v>699300</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3">
         <v>792700</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z22" s="3">
         <v>863500</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="3">
         <v>747600</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD22" s="3">
         <v>720300</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF22" s="3">
         <v>791700</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1975,71 +2017,74 @@
       <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>-365500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-194900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-280700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-100100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4843800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>200300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-68900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-245500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>506700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>300000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>969800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>734200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>708600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>562300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1331700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>354100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2023900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1501900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>992600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>431500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>731300</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2064,71 +2109,74 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>2175300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2223000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>111000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>54400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4213900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-38800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-7500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-40200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-6105100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-240800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>181100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>89500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>141300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>129800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>461100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>130400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>82800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-56500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>326100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>171300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>36200</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,8 +2264,11 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2242,71 +2293,74 @@
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>-2540800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2417900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-391700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-154500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9057700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>239100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-61400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-205300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6611800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>540700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>788700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>644700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>567400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>432400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>870500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>223700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2106700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1445400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>666500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>260200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2331,71 +2385,74 @@
       <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>-2704800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2486600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-525600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-222000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9231100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>149700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-160500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-228500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6529000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>519000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>739600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>610900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>407400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>368700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>648200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>197400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>584100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>220700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2509,8 +2569,8 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2533,11 +2593,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2546,11 +2606,11 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>18700</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
@@ -2572,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2776,71 +2845,74 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-170600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>240300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>29400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>327500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-173500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>290800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-42000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>293100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-44900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>307200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-532400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-152700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>448300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>24700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>462900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>364400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>59300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>383200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>36200</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2865,71 +2937,74 @@
       <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>-2704800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2486600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-525600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-222000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9231100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>149700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-160500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-228500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6529000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>519000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>739600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>610900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>426100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>368700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>648200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>197400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>584100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>220700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,8 +3092,11 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3043,165 +3121,171 @@
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>-2704800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2486600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-525600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-222000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9231100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>149700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-160500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-228500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6529000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>519000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>739600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>610900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>426100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>368700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>648200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>197400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>584100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>220700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,809 +3351,837 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3027200</v>
+      </c>
+      <c r="E41" s="3">
         <v>2413600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>595700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1386300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3218700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3483300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2603700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2890000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3937500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3897600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2601600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3560300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7484600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4784700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5351100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4623500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4816400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2966300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3930500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3561800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3663300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2630100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1999900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2515600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2267600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2816600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2308000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1844600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3925400</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1593300</v>
+      </c>
+      <c r="E42" s="3">
         <v>2094600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2237200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1929000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2272600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1928500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2036000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1824200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1772200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2112200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2048900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2308900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2592100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1643300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1573400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3134900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1250700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1293200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1098500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1074500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1166200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1527600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1307000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1882800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1651300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1694600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1564700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1831500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1570100</v>
       </c>
     </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4582300</v>
+      </c>
+      <c r="E43" s="3">
         <v>5261000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3594800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6108500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4708700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5289000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3777300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5167300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3950800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5447200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3698500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4971500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3694600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4720100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3787500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4649900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3621600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4836600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4119300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5433800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4973200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6253600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4826800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6313500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4907900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5703000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4508400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5900700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4597300</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>307500</v>
+      </c>
+      <c r="E44" s="3">
         <v>350200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>331100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>418600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>381300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>385300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>411600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>394400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>356600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>381000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>352500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>336200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>305700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>385500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>366100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>350200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>286300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>282300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>279300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>307600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>303500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>366300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>371700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>388800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>460100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>344500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>352500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>357900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>318400</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>25672300</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>1444700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1611400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>1315800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>1360100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>1176200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>1005800</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T45" s="3">
         <v>853800</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V45" s="3">
         <v>1030900</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W45" s="3">
+      <c r="W45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X45" s="3">
         <v>938600</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z45" s="3">
         <v>1203500</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB45" s="3">
         <v>1038600</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD45" s="3">
         <v>1109000</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF45" s="3">
         <v>932200</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9510300</v>
+      </c>
+      <c r="E46" s="3">
         <v>10119300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32431200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9842500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12026100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11087000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10440000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10276000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11333000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11838000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10061700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11177000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15253300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11533600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12083900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12758400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>10762900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9378500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10458600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10377800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11044900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10777500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9708800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11100700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10325500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10558800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9842500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9934700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>11343400</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>429700</v>
+      </c>
+      <c r="E47" s="3">
         <v>1502300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1340400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1891300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1923300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1857500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1994500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2495700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1585000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5714100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1270900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8292400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4296300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7922800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3883300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7397500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3628500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7896300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4272000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9769100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3208000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6742300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3669200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5077900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2973800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3953000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2599000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4036200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3033800</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8310400</v>
+      </c>
+      <c r="E48" s="3">
         <v>8917000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8012400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21752100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22335600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20854100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21637600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21337500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21695700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21641400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21245200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20531400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19685100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19160200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19327100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>18865200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>18085900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>18349000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19645100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20250600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>22770300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>24117600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>23400900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>23709900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>19099100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>17481300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>17492200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17704200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18168600</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17642600</v>
+      </c>
+      <c r="E49" s="3">
         <v>19252700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18791400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>28183200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>29061600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>27973100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>29126600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>28971100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>29647100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>29826600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>29278600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>28359200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>27877600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>31416400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>31655500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>30996200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>29510100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>30568200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>32440400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>32756800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>35897900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>42218100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>40927000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>41849100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>42179800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>37227500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>39297400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>39766300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>40246100</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,97 +4361,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2527200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1777800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2852200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2368100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>475300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2436500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>792600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2602100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4440400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>877200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10577400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3775700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7893300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8560300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12529700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7984700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11035200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1120900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5791600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1022200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8919000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1248300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3597400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1498800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3106300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1190700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2232200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>991500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2731800</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>38992600</v>
+      </c>
+      <c r="E54" s="3">
         <v>42229500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>65424800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>64912100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>68706800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>65164100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>66953100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>66580800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>68701100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>69897300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>72433700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>72135600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>75005600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>78593200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>79479500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>78002100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>73022600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>67313000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>72607700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>74176400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>81840100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>85103700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>81303400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>83236400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>77620700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>70411200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>71463300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>72432900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>75523700</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,542 +4707,561 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7323700</v>
+      </c>
+      <c r="E57" s="3">
         <v>7694600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3896900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9767000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6014100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8355200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5253300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8712500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5864700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8407800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4971500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10505600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5595000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8740100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4093300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7438800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4122300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6131900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3279300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7170600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5046700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7912200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4031500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>8182000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5287600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>6761900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3978100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>7476300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5100200</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4548100</v>
+      </c>
+      <c r="E58" s="3">
         <v>4255000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14453000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5916500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7305200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7348600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9137600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6526500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6235800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6218100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4662500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4146700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7044500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5442700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5541700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6075000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4233000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4583400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4700700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4584000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4388300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5239300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4011500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6679600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6594700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7155100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>6297000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>5512000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>5139700</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E59" s="3">
         <v>23400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11864400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2823000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1748900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>46700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3563100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5817000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>297100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5100700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>261700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3603300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>269800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2761800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>58100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3511600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>46900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3550100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>51400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3972700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>77800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3354700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>47600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3631100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>81300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3362100</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11917400</v>
+      </c>
+      <c r="E60" s="3">
         <v>11973000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32086100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15708300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17707500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15730300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18059000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15285700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15663700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14635800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15451000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14949400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17740200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14444500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13238300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13783600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11117000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10773400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11491600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11801500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12985100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>13202900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12015700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14939300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>15236900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>13964600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>13906200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>13069500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>13602000</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11542600</v>
+      </c>
+      <c r="E61" s="3">
         <v>13305800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14091900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>27997600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>28768700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27484100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>25672500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28097600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28862900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>30465600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>28256900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28920600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28346000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>27642900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>26142800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>26892200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>25944400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>28929400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>29868000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>32482900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>33295700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>37070600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>33809700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>35096500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>27956700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>27723200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>25709700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28833500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28755500</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1429800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1361800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1010400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2198700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1434700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2012100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1303500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2221900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3434700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3584200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4216400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3527600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5027000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3509600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7147400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5774600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7196200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5323400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7909100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5880000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>9145500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7214000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>9204200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7100600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8702600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4465800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6158700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4571000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7052500</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25160000</v>
+      </c>
+      <c r="E66" s="3">
         <v>26950700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47760600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>46563800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>49349000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>46322000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47014200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>46840500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52019500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52772700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>53294000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>52782600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>56127100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>50548600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>51473700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>51146900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>46875800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>46319400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>50701100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>51678600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>58165000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>60332000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>57835400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>59776500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>54521000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>48500700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>48032000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>48898300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>51854100</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,8 +6027,11 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5871,83 +6044,86 @@
       <c r="F72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3">
         <v>-1592800</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>3835600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4038300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6418700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6722300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6912200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16264400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16093200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15713400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15440700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9793600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9747300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9963300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9994200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>10410000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9644100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9345900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9238400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9251800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>10729700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10540800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10403600</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12379100</v>
+      </c>
+      <c r="E76" s="3">
         <v>13659400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13652600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14237800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15083500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14809500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15751100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15713800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16681600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17124600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19139700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19352900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18878500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>28044600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>28005900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>26855200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>26146800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20993600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>21906600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>22497800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>23675100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>24771700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>23468000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>23459900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>23099700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>21910500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>23431300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>23534500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>23669600</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,102 +6579,108 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6511,71 +6705,74 @@
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>-2704800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2486600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-525600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-222000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9231100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>149700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-160500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-228500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6529000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>519000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>739600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>610900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>426100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>368700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>648200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>197400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>584100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>220700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,97 +6804,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>1348500</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>1304900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1322000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1220800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>474600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1229700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2749100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1379000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2497200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1204500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2408900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1232000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2442400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1195500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2262100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1177000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2561500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1310200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2838000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1545900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2936300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1512000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2523100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1157400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2330000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1158400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2442000</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>998000</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>415400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1557400</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>924600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2660500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1120900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2712600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1169700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2613800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1117800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2073000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1334100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2514400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1574500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4396400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2585500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3281600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1699100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3692700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1776400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2382400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1032300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2830600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1021100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2482600</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,97 +7482,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
+      <c r="D91" s="3">
+        <v>-392400</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1160900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1334100</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1145200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1003000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2713000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1438000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1151000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2364000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-872000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1187000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-924700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1275700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2787800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-90500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1239300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1778000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-937100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2501000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-61000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2622500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-674200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-536900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3041500</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>184300</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>-704500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1236900</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1254900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2559700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1699100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3290400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-822600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3139600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1165200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2391800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-889800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1457200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-994300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1762900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1220700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1480300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1075500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2337500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1498800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2488800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1073300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2426600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1653600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2909700</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,97 +7884,101 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
+      <c r="D96" s="3">
+        <v>42400</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>42100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>27600</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>41300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-34300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-17700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-40300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-28300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-34700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-361800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-25400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-33900</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-388400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-43600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-38500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-7300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-289400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-29900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-40200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-18800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-243800</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-18700</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,271 +8250,283 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>-242300</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>-1461900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-725100</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3">
         <v>-647500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1220600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1824200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4320800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4462300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2662500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-483500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>762400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-576600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-144600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1498700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2033500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1206500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-29200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-128600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1281100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>279900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-432900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>548300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1607500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1103500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-429300</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>-11100</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3">
         <v>4300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-34200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>10800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-170400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>160000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-23300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>12200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-20700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>156700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-37900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>51700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-14800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-9000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-9300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-163600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-90500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-17500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>7200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-14200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-16600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-56000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-65900</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>902800</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1755300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-415600</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-973500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1298100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1258200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4919300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3958500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2098800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-568600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>495400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-147100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>903600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-927900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>436400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>67600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1754600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>491200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>80000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>564600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-553600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>490700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1259400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1756800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-922300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>TIIAY</t>
   </si>
@@ -656,140 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -817,71 +821,74 @@
       <c r="K8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>9116700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4399400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8222800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3965000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8400700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4089000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8123100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3969600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8025100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4045700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8464400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4324400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10483300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5425500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10580500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5348200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11236400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5134800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10333300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5144100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11041500</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -909,71 +916,74 @@
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>3961900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1834200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3323100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1589700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3510300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1619700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3007800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1478000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3054000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1499800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2782900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1388700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3552400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1755400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3517400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1818200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1594500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1979300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6005000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1977500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1573400</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1001,71 +1011,74 @@
       <c r="K10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>5154800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2565200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4899700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2375300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4890400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2469300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5115300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2491600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4971000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2546000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5681500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2935600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6930900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3670100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>7063100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3530000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9641800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3155600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4328300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3166600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>9468100</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1311,71 +1331,74 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>74200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>334500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>317700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>77300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4467600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>60300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>482500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>424300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>155600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>43600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>111300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>26200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>440100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>39200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-408200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>23900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3320400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2228500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>166900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>800400</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1403,71 +1426,74 @@
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="3">
         <v>2749100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1379000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2497200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1204500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2408900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1230900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2442400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1195500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2262100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1177000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2561500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1310200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2838000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1545900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2936300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1512000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2523100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1157400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2330000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1158400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>2442000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,8 +1523,9 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1526,71 +1553,74 @@
       <c r="K17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>8885200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4354000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7790800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3737600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12769600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3597900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7601800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3922000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6965800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3438600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7327600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3742900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8979700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4414900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8360700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4531200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>12517400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6272300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8561100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4329400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9482300</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1618,71 +1648,74 @@
       <c r="K18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>231500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>45400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>432000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>227400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4368900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>491100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>521200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>47600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1059200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>607200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1136700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>581500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1503600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1010600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2219900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>817000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1281100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1137500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1772200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>814700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1559200</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1748,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1744,71 +1778,74 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>170600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-240300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-29400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-327500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>173500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-290800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>42000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-293100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>44900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-307200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>532400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>152700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-448300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-24700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-462900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-364400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-59300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-383200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-36200</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1836,71 +1873,74 @@
       <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3">
         <v>3151100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1184000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2899800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1104400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1786600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1432300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3005600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>950100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3366200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1476900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4230500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2044400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4339300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2108200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5131500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1866100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1246800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-344500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4042800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1589900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3964900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1928,71 +1968,74 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>767600</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>683300</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3">
         <v>648300</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
         <v>632100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U22" s="3">
         <v>597400</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3">
         <v>699300</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="3">
         <v>792700</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3">
         <v>863500</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC22" s="3">
         <v>747600</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE22" s="3">
         <v>720300</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG22" s="3">
         <v>791700</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2020,71 +2063,74 @@
       <c r="K23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>-365500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-194900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-280700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-100100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4843800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>200300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-68900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-245500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>506700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>300000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>969800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>734200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>708600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>562300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1331700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>354100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2023900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1501900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>992600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>431500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>731300</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2112,71 +2158,74 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>2175300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2223000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>111000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>54400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4213900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-38800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-7500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-40200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-6105100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-240800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>181100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>89500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>141300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>129800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>461100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>130400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>82800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-56500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>326100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>171300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>36200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,8 +2316,11 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2296,71 +2348,74 @@
       <c r="K26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>-2540800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2417900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-391700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-154500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9057700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>239100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-61400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-205300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6611800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>540700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>788700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>644700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>567400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>432400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>870500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>223700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2106700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1445400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>666500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>260200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2388,71 +2443,74 @@
       <c r="K27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>-2704800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2486600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-525600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-222000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9231100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>149700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-160500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-228500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6529000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>519000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>739600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>610900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>407400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>368700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>648200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>197400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>584100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>220700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2633,8 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2596,11 +2657,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2609,11 +2670,11 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>18700</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2886,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2848,71 +2918,74 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-170600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>240300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>29400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>327500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-173500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>290800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-42000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>293100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-44900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>307200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-532400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-152700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>448300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>24700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>462900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>364400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>59300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>383200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>36200</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2940,71 +3013,74 @@
       <c r="K33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>-2704800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2486600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-525600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-222000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9231100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>149700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-160500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-228500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6529000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>519000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>739600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>610900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>426100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>368700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>648200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>197400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>584100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>220700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,8 +3171,11 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3124,168 +3203,174 @@
       <c r="K35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>-2704800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2486600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-525600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-222000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9231100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>149700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-160500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-228500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6529000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>519000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>739600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>610900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>426100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>368700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>648200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>197400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>584100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>220700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,836 +3438,864 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2407000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3027200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2413600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>595700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1386300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3218700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3483300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2603700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2890000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3937500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3897600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2601600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3560300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7484600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4784700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5351100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4623500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4816400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2966300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3930500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3561800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3663300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2630100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1999900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2515600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2267600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2816600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2308000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1844600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3925400</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1593300</v>
+        <v>1684000</v>
       </c>
       <c r="E42" s="3">
+        <v>1704100</v>
+      </c>
+      <c r="F42" s="3">
         <v>2094600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2237200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1929000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2272600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1928500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2036000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1824200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1772200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2112200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2048900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2308900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2592100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1643300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1573400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3134900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1250700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1293200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1098500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1074500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1166200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1527600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1307000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1882800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1651300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1694600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1564700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1831500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1570100</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4582300</v>
+        <v>5379400</v>
       </c>
       <c r="E43" s="3">
+        <v>3363700</v>
+      </c>
+      <c r="F43" s="3">
         <v>5261000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3594800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6108500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4708700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5289000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3777300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5167300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3950800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5447200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3698500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4971500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3694600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4720100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3787500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4649900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3621600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4836600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4119300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5433800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4973200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6253600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4826800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6313500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4907900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5703000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4508400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5900700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4597300</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>241000</v>
+      </c>
+      <c r="E44" s="3">
         <v>307500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>350200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>331100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>418600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>381300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>385300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>411600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>394400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>356600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>381000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>352500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>336200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>305700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>385500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>366100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>350200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>286300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>282300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>279300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>307600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>303500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>366300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>371700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>388800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>460100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>344500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>352500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>357900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>318400</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3">
+        <v>1264600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1107800</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>25672300</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>1444700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1611400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>1315800</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>1360100</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1176200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S45" s="3">
         <v>1005800</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U45" s="3">
         <v>853800</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W45" s="3">
         <v>1030900</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y45" s="3">
         <v>938600</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="3">
         <v>1203500</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3">
         <v>1038600</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE45" s="3">
         <v>1109000</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG45" s="3">
         <v>932200</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10976000</v>
+      </c>
+      <c r="E46" s="3">
         <v>9510300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10119300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>32431200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9842500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12026100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11087000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10440000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10276000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11333000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11838000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10061700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11177000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15253300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11533600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12083900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12758400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10762900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9378500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10458600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10377800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11044900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10777500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9708800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>11100700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10325500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10558800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9842500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9934700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>11343400</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>429700</v>
+        <v>443100</v>
       </c>
       <c r="E47" s="3">
+        <v>1087100</v>
+      </c>
+      <c r="F47" s="3">
         <v>1502300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1340400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1891300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1923300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1857500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1994500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2495700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1585000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5714100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1270900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8292400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4296300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7922800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3883300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7397500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3628500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7896300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4272000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9769100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3208000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6742300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3669200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>5077900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2973800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3953000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2599000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4036200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3033800</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8186300</v>
+      </c>
+      <c r="E48" s="3">
         <v>8310400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8917000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8012400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21752100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22335600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20854100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21637600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21337500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21695700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21641400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21245200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20531400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19685100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19160200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19327100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>18865200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>18085900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>18349000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19645100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20250600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>22770300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>24117600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>23400900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>23709900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19099100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>17481300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17492200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17704200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>18168600</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18334400</v>
+      </c>
+      <c r="E49" s="3">
         <v>17642600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19252700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18791400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>28183200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>29061600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>27973100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>29126600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>28971100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>29647100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>29826600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>29278600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>28359200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>27877600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>31416400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>31655500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>30996200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>29510100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>30568200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>32440400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>32756800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>35897900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>42218100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>40927000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>41849100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>42179800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>37227500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>39297400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>39766300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>40246100</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2527200</v>
+        <v>2471900</v>
       </c>
       <c r="E52" s="3">
+        <v>576700</v>
+      </c>
+      <c r="F52" s="3">
         <v>1777800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2852200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2368100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>475300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2436500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>792600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2602100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4440400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>877200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10577400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3775700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7893300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8560300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12529700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7984700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11035200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1120900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5791600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1022200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8919000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1248300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3597400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1498800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3106300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1190700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2232200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>991500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2731800</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>41021400</v>
+      </c>
+      <c r="E54" s="3">
         <v>38992600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42229500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>65424800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>64912100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>68706800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>65164100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>66953100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>66580800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>68701100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>69897300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>72433700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>72135600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>75005600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>78593200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>79479500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>78002100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>73022600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>67313000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>72607700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>74176400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>81840100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>85103700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>81303400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>83236400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>77620700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>70411200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>71463300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>72432900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>75523700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4838,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>7323700</v>
+        <v>7442700</v>
       </c>
       <c r="E57" s="3">
+        <v>4504600</v>
+      </c>
+      <c r="F57" s="3">
         <v>7694600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3896900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9767000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6014100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8355200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5253300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8712500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5864700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8407800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4971500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10505600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5595000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8740100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4093300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7438800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4122300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6131900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3279300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7170600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5046700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7912200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4031500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>8182000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5287600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6761900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3978100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>7476300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5100200</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4856200</v>
+      </c>
+      <c r="E58" s="3">
         <v>4548100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4255000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>14453000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5916500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7305200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7348600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9137600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6526500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6235800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6218100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4662500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4146700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7044500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5442700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5541700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6075000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4233000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4583400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4700700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4584000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4388300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5239300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4011500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6679600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6594700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7155100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>6297000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>5512000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>5139700</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>45600</v>
+        <v>1134900</v>
       </c>
       <c r="E59" s="3">
+        <v>1666800</v>
+      </c>
+      <c r="F59" s="3">
         <v>23400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11864400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2823000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1748900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>46700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3563100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5817000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>297100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5100700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>261700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3603300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>269800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2761800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>58100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3511600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>46900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3550100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>51400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3972700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>77800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3354700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>47600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3631100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>81300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3362100</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13433900</v>
+      </c>
+      <c r="E60" s="3">
         <v>11917400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11973000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32086100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15708300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17707500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15730300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18059000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15285700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15663700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14635800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15451000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14949400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17740200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14444500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13238300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13783600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11117000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10773400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11491600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11801500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12985100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>13202900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12015700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>14939300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>15236900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>13964600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>13906200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>13069500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>13602000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11569400</v>
+      </c>
+      <c r="E61" s="3">
         <v>11542600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>13305800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14091900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>27997600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>28768700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>27484100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25672500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28097600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>28862900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>30465600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28256900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28920600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>28346000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>27642900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>26142800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>26892200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>25944400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>28929400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>29868000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>32482900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>33295700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>37070600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>33809700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>35096500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>27956700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>27723200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>25709700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28833500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28755500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1429800</v>
+        <v>1341300</v>
       </c>
       <c r="E62" s="3">
+        <v>909000</v>
+      </c>
+      <c r="F62" s="3">
         <v>1361800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1010400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2198700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1434700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2012100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1303500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2221900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3434700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3584200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4216400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3527600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5027000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3509600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7147400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5774600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7196200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5323400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7909100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5880000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9145500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7214000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9204200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7100600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8702600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4465800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6158700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4571000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7052500</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26621300</v>
+      </c>
+      <c r="E66" s="3">
         <v>25160000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26950700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47760600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>46563800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>49349000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>46322000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>47014200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>46840500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52019500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52772700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53294000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>52782600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>56127100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>50548600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>51473700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>51146900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>46875800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>46319400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>50701100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>51678600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>58165000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>60332000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>57835400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>59776500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>54521000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>48500700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>48032000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>48898300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>51854100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,16 +6201,19 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>8</v>
+      <c r="E72" s="3">
+        <v>-631500</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>8</v>
@@ -6047,83 +6221,86 @@
       <c r="G72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3">
         <v>-1592800</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3">
         <v>3835600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4038300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6418700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6722300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6912200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16264400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16093200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15713400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15440700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9793600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9747300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9963300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9994200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10410000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9644100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9345900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9238400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9251800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10729700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10540800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>10403600</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12943100</v>
+      </c>
+      <c r="E76" s="3">
         <v>12379100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13659400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13652600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14237800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15083500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14809500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15751100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15713800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16681600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17124600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19139700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19352900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18878500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>28044600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>28005900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>26855200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>26146800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20993600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21906600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>22497800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>23675100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>24771700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>23468000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>23459900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>23099700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>21910500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>23431300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>23534500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>23669600</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,105 +6771,111 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6708,71 +6903,74 @@
       <c r="K81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>-2704800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2486600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-525600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-222000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9231100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>149700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-160500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-228500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6529000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>519000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>739600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>610900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>426100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>368700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>648200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>197400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>584100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>220700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7003,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1348500</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
+        <v>1264400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>903100</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3">
         <v>1304900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1322000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1220800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>474600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1229700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2749100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1379000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2497200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1204500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2408900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1232000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2442400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1195500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2262100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1177000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2561500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1310200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2838000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1545900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2936300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1512000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2523100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1157400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2330000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1158400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2442000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>998000</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>8</v>
+        <v>322100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1590200</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G89" s="3">
-        <v>415400</v>
+      <c r="G89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H89" s="3">
-        <v>1557400</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
+        <v>477900</v>
+      </c>
+      <c r="I89" s="3">
+        <v>1626000</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>924600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2660500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1120900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2712600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1169700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2613800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1117800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2073000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1334100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2514400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1574500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4396400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2585500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3281600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1699100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3692700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1776400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2382400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1032300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2830600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1021100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2482600</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7703,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-591200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-392400</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="3">
-        <v>-1160900</v>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H91" s="3">
-        <v>-1334100</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
+        <v>-1136000</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-613500</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1145200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1003000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2713000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1438000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1151000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2364000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-872000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1187000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-924700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1275700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2787800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-90500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1239300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1778000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-937100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2501000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-61000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2622500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-674200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-536900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3041500</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>184300</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
+        <v>-605300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-251600</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G94" s="3">
-        <v>-704500</v>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H94" s="3">
-        <v>-1236900</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
+        <v>-695900</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-1091000</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3">
         <v>-1254900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2559700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1699100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3290400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-822600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3139600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1165200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2391800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-889800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1457200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-994300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1762900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1220700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1480300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1075500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2337500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1498800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2488800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1073300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2426600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1653600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2909700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,100 +8118,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E96" s="3">
         <v>42400</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
         <v>42100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>27600</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>41300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-34300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-17700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-40300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-28300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-34700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-19400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-361800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-25400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-33900</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-388400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-43600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-38500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-289400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-29900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-40200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-18800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-243800</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-18700</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8496,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-242300</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
+        <v>-452900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-398600</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G100" s="3">
-        <v>-1461900</v>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H100" s="3">
-        <v>-725100</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
+        <v>-1533100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-939500</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3">
         <v>-647500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1220600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1824200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4320800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4462300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2662500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-483500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>762400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-576600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-144600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1498700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2033500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1206500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-29200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-128600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1281100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>279900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-432900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>548300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1607500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1103500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-429300</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-11100</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3">
         <v>4300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-34200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>10800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-170400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>160000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-23300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>12200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-20700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>156700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-37900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-37700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>51700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-14800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-9000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-9300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-163600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-90500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-17500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>5900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>7200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-16600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-56000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-65900</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-717700</v>
+      </c>
+      <c r="E102" s="3">
         <v>902800</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-1755300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-415600</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-973500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1298100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1258200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4919300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3958500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2098800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-568600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>495400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-147100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>903600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-927900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>436400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>67600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1754600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>491200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>80000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>564600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-553600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>490700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1259400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1756800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-922300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
   <si>
     <t>TIIAY</t>
   </si>
@@ -656,144 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -824,71 +828,74 @@
       <c r="L8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>9116700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4399400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8222800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3965000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8400700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4089000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8123100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3969600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8025100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4045700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8464400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4324400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10483300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5425500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10580500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5348200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11236400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5134800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10333300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5144100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>11041500</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -919,71 +926,74 @@
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>3961900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1834200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3323100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1589700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3510300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1619700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3007800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1478000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3054000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1499800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2782900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1388700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3552400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1755400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3517400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1818200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1594500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1979300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6005000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1977500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1573400</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1014,71 +1024,74 @@
       <c r="L10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>5154800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2565200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4899700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2375300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4890400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2469300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5115300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2491600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4971000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2546000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5681500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2935600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6930900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3670100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>7063100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3530000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9641800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3155600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4328300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3166600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>9468100</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1319,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1334,71 +1354,74 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>74200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>334500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>317700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>77300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4467600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>60300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>482500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>424300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>155600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>43600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>111300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>26200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>440100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>39200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-408200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>23900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>3320400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2228500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>166900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>800400</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1429,71 +1452,74 @@
       <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="3">
         <v>2749100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1379000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2497200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1204500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2408900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1230900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2442400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1195500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2262100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1177000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2561500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1310200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2838000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1545900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2936300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1512000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2523100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1157400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2330000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1158400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>2442000</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,8 +1550,9 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1556,71 +1583,74 @@
       <c r="L17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>8885200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4354000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7790800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3737600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12769600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3597900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7601800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3922000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6965800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3438600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7327600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3742900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8979700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4414900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8360700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4531200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12517400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6272300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8561100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4329400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9482300</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1651,71 +1681,74 @@
       <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>231500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>45400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>432000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>227400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4368900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>491100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>521200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>47600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1059200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>607200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1136700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>581500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1503600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1010600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2219900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>817000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1281100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1137500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1772200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>814700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1559200</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1782,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1781,71 +1815,74 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>170600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-240300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-29400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-327500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>173500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-290800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>42000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-293100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>44900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-307200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>532400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>152700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-448300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-24700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-462900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-364400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-59300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-383200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-36200</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1876,71 +1913,74 @@
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>3151100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1184000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2899800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1104400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1786600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1432300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3005600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>950100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3366200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1476900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4230500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2044400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4339300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2108200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5131500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1866100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1246800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-344500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4042800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1589900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3964900</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1971,71 +2011,74 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>767600</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3">
         <v>683300</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>648300</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3">
         <v>632100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V22" s="3">
         <v>597400</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3">
         <v>699300</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z22" s="3">
         <v>792700</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="3">
         <v>863500</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD22" s="3">
         <v>747600</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF22" s="3">
         <v>720300</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH22" s="3">
         <v>791700</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2066,71 +2109,74 @@
       <c r="L23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>-365500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-194900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-280700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-100100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4843800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>200300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-68900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-245500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>506700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>300000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>969800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>734200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>708600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>562300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1331700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>354100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2023900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1501900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>992600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>431500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>731300</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2161,71 +2207,74 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>2175300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2223000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>111000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>54400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4213900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-38800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-7500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-40200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-6105100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-240800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>181100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>89500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>141300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>129800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>461100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>130400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>82800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-56500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>326100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>171300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>36200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,8 +2368,11 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2351,71 +2403,74 @@
       <c r="L26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>-2540800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2417900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-391700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-154500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9057700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>239100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-61400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-205300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6611800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>540700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>788700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>644700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>567400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>432400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>870500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>223700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2106700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1445400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>666500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>260200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2446,71 +2501,74 @@
       <c r="L27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>-2704800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2486600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-525600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-222000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9231100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>149700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-160500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-228500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6529000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>519000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>739600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>610900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>407400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>368700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>648200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>197400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>584100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>220700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2636,8 +2697,8 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2660,11 +2721,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2673,11 +2734,11 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>18700</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +2956,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2921,71 +2991,74 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>-170600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>240300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>29400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>327500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-173500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>290800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-42000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>293100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-44900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>307200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-532400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-152700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>448300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>24700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>462900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>364400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>59300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>383200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>36200</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3016,71 +3089,74 @@
       <c r="L33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>-2704800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2486600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-525600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-222000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9231100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>149700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-160500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-228500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6529000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>519000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>739600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>610900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>426100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>368700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>648200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>197400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>584100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>220700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,8 +3250,11 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3206,171 +3285,177 @@
       <c r="L35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>-2704800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2486600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-525600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-222000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9231100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>149700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-160500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-228500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6529000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>519000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>739600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>610900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>426100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>368700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>648200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>197400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>584100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>220700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,863 +3525,891 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1693500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2407000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3027200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2413600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>595700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1386300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3218700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3483300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2603700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2890000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3937500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3897600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2601600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3560300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7484600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4784700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5351100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4623500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4816400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2966300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3930500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3561800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3663300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2630100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1999900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2515600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2267600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2816600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2308000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1844600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3925400</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1814400</v>
+      </c>
+      <c r="E42" s="3">
         <v>1684000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1704100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2094600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2237200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1929000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2272600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1928500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2036000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1824200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1772200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2112200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2048900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2308900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2592100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1643300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1573400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3134900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1250700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1293200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1098500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1074500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1166200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1527600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1307000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1882800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1651300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1694600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1564700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1831500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1570100</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5708700</v>
+      </c>
+      <c r="E43" s="3">
         <v>5379400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3363700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5261000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3594800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6108500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4708700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5289000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3777300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5167300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3950800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5447200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3698500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4971500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3694600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4720100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3787500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4649900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3621600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4836600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4119300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5433800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4973200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6253600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4826800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6313500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4907900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5703000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4508400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5900700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4597300</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>267800</v>
+      </c>
+      <c r="E44" s="3">
         <v>241000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>307500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>350200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>331100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>418600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>381300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>385300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>411600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>394400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>356600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>381000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>352500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>336200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>305700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>385500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>366100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>350200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>286300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>282300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>279300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>307600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>303500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>366300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>371700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>388800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>460100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>344500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>352500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>357900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>318400</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1337600</v>
+      </c>
+      <c r="E45" s="3">
         <v>1264600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1107800</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>25672300</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>1444700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1611400</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>1315800</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>1360100</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>1176200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T45" s="3">
         <v>1005800</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V45" s="3">
         <v>853800</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W45" s="3">
+      <c r="W45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X45" s="3">
         <v>1030900</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z45" s="3">
         <v>938600</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB45" s="3">
         <v>1203500</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD45" s="3">
         <v>1038600</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF45" s="3">
         <v>1109000</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH45" s="3">
         <v>932200</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10822100</v>
+      </c>
+      <c r="E46" s="3">
         <v>10976000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9510300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10119300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>32431200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9842500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12026100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11087000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10440000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10276000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11333000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11838000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10061700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11177000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15253300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11533600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12083900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12758400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10762900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9378500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10458600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10377800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11044900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10777500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9708800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>11100700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10325500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10558800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9842500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9934700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>11343400</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>963000</v>
+      </c>
+      <c r="E47" s="3">
         <v>443100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1087100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1502300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1340400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1891300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1923300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1857500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1994500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2495700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1585000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5714100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1270900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8292400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4296300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7922800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3883300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7397500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3628500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7896300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4272000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>9769100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3208000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6742300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3669200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5077900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2973800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3953000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2599000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4036200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3033800</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8716400</v>
+      </c>
+      <c r="E48" s="3">
         <v>8186300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8310400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8917000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8012400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21752100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22335600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20854100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21637600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21337500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21695700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21641400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21245200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20531400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19685100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19160200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19327100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>18865200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>18085900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18349000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19645100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20250600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>22770300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>24117600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>23400900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>23709900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19099100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17481300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17492200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17704200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18168600</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19627700</v>
+      </c>
+      <c r="E49" s="3">
         <v>18334400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17642600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19252700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18791400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>28183200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>29061600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>27973100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>29126600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>28971100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>29647100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>29826600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>29278600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>28359200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>27877600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>31416400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>31655500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>30996200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>29510100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>30568200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>32440400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>32756800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>35897900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>42218100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>40927000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>41849100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>42179800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>37227500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>39297400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>39766300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>40246100</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4601,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2025800</v>
+      </c>
+      <c r="E52" s="3">
         <v>2471900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>576700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1777800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2852200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2368100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>475300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2436500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>792600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2602100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4440400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>877200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10577400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3775700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7893300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8560300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12529700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7984700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11035200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1120900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5791600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1022200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8919000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1248300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3597400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1498800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3106300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1190700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2232200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>991500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2731800</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4797,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42803300</v>
+      </c>
+      <c r="E54" s="3">
         <v>41021400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>38992600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42229500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>65424800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>64912100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>68706800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>65164100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>66953100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>66580800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>68701100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>69897300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>72433700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>72135600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>75005600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>78593200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>79479500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>78002100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>73022600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>67313000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>72607700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>74176400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>81840100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>85103700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>81303400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>83236400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>77620700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>70411200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>71463300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>72432900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>75523700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,578 +4969,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>7442700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4504600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7694600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3896900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9767000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6014100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8355200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5253300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8712500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5864700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8407800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4971500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10505600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5595000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8740100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4093300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7438800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4122300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6131900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3279300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7170600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5046700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7912200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4031500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8182000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5287600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6761900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3978100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>7476300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5100200</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5234300</v>
+      </c>
+      <c r="E58" s="3">
         <v>4856200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4548100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4255000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>14453000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5916500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7305200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7348600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9137600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6526500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6235800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6218100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4662500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4146700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7044500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5442700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5541700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6075000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4233000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4583400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4700700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4584000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4388300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5239300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4011500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6679600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>6594700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7155100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>6297000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>5512000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>5139700</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3204900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1134900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1666800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11864400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2823000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>26500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1748900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>46700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3563100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5817000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>297100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5100700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>261700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3603300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>269800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2761800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>58100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3511600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>46900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3550100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>51400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3972700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>77800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3354700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>47600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3631100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>81300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3362100</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14391100</v>
+      </c>
+      <c r="E60" s="3">
         <v>13433900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11917400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11973000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32086100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15708300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17707500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15730300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18059000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15285700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15663700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14635800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15451000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14949400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17740200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14444500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13238300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13783600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11117000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10773400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11491600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11801500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12985100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>13202900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12015700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>14939300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>15236900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>13964600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>13906200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>13069500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>13602000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11389300</v>
+      </c>
+      <c r="E61" s="3">
         <v>11569400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11542600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>13305800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14091900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27997600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>28768700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>27484100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25672500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>28097600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>28862900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>30465600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28256900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>28920600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>28346000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>27642900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>26142800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>26892200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>25944400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>28929400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>29868000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>32482900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>33295700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>37070600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>33809700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>35096500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>27956700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>27723200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>25709700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28833500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>28755500</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>811500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1341300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>909000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1361800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1010400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2198700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1434700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2012100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1303500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2221900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3434700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3584200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4216400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3527600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5027000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3509600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7147400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5774600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7196200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5323400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7909100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5880000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>9145500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7214000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9204200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7100600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8702600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4465800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6158700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4571000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7052500</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5849,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27302400</v>
+      </c>
+      <c r="E66" s="3">
         <v>26621300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25160000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26950700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>47760600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>46563800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>49349000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>46322000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>47014200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>46840500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52019500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>52772700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>53294000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>52782600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>56127100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>50548600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>51473700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>51146900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>46875800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>46319400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>50701100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>51678600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>58165000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>60332000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>57835400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>59776500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>54521000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>48500700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>48032000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>48898300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>51854100</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6375,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3">
         <v>-631500</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3">
         <v>-1592800</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" s="3">
         <v>3835600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4038300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6418700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6722300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6912200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16264400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16093200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15713400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15440700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9793600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9747300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9963300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9994200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10410000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9644100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9345900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9238400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9251800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10729700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>10540800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>10403600</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6767,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13927200</v>
+      </c>
+      <c r="E76" s="3">
         <v>12943100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12379100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13659400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13652600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14237800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15083500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14809500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15751100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15713800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16681600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17124600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19139700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19352900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18878500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>28044600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>28005900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>26855200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>26146800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>20993600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21906600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>22497800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>23675100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>24771700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>23468000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>23459900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>23099700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>21910500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>23431300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>23534500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>23669600</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,108 +6963,114 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6906,71 +7101,74 @@
       <c r="L81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>-2704800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2486600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-525600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-222000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9231100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>149700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-160500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-228500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6529000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>519000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>739600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>610900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>426100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>368700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>648200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>197400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>584100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>220700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,103 +7202,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>426400</v>
+      </c>
+      <c r="E83" s="3">
         <v>1264400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>903100</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3">
         <v>1304900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1322000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1220800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>474600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1229700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2749100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1379000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2497200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1204500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2408900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1232000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2442400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1195500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2262100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1177000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2561500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1310200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2838000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1545900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2936300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1512000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2523100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1157400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2330000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1158400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2442000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>709300</v>
+      </c>
+      <c r="E89" s="3">
         <v>322100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1590200</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H89" s="3">
+        <v>243200</v>
+      </c>
+      <c r="I89" s="3">
         <v>477900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1626000</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M89" s="3">
         <v>924600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2660500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1120900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2712600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1169700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2613800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1117800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2073000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1334100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2514400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1574500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4396400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2585500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3281600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1699100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3692700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1776400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2382400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1032300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2830600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1021100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2482600</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +7924,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-468600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-591200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-392400</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H91" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1136000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-613500</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1145200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1003000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2713000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1438000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1151000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2364000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-872000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1187000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-924700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1275700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2787800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-90500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1239300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1778000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-937100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2501000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-61000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2622500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-674200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-536900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3041500</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8216,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-374600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-605300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-251600</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H94" s="3">
+        <v>-148900</v>
+      </c>
+      <c r="I94" s="3">
         <v>-695900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1091000</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M94" s="3">
         <v>-1254900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2559700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1699100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3290400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-822600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3139600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1165200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2391800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-889800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1457200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-994300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1762900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1220700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1480300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1075500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2337500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1498800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2488800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1073300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2426600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1653600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2909700</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,103 +8352,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E96" s="3">
         <v>37800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>42400</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H96" s="3">
+        <v>50400</v>
+      </c>
+      <c r="I96" s="3">
         <v>42100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>27600</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>41300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-34300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-17700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-40300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-34700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-19400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-361800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-25400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-33900</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-388400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-43600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-38500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-7300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-289400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-29900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-40200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-18800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-243800</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-18700</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,289 +8742,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1239000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-452900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-398600</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H100" s="3">
+        <v>-789700</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1533100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-939500</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M100" s="3">
         <v>-647500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1220600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1824200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4320800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4462300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2662500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-483500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>762400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-576600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-144600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1498700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2033500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1206500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-29200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-128600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1281100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>279900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-432900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>548300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1607500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1103500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-429300</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-42900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-11100</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3">
         <v>4300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-34200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>10800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-170400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>160000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-23300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>12200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-20700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>156700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-37900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-37700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>51700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-14800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-9000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-9300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-163600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-90500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-17500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>7200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-14200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-56000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-65900</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-925400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-717700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>902800</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>-738200</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1755300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-415600</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-973500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1298100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1258200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4919300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3958500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2098800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-568600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>495400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-147100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>903600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-927900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>436400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>67600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1754600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>491200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>80000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>564600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-553600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>490700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1259400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1756800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-922300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>TIIAY</t>
   </si>
@@ -7419,8 +7419,8 @@
       <c r="G83" s="3">
         <v>903100</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
+      <c r="H83" s="3">
+        <v>873200</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>8</v>
@@ -9109,8 +9109,8 @@
       <c r="G101" s="3">
         <v>-11100</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>8</v>
+      <c r="H101" s="3">
+        <v>-5300</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>8</v>

--- a/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TIIAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
   <si>
     <t>TIIAY</t>
   </si>
@@ -656,152 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -838,71 +845,77 @@
       <c r="N8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="3">
         <v>9116700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4399400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>8222800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3965000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>8400700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>4089000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>8123100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3969600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>8025100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>4045700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>8464400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>4324400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>10483300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>5425500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>10580500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>5348200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>11236400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>5134800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>10333300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>5144100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>11041500</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -939,71 +952,77 @@
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="3">
         <v>3961900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1834200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3323100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1589700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>3510300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1619700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3007800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1478000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>3054000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1499800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2782900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1388700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>3552400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1755400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>3517400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1818200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>1594500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1979300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>6005000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>1977500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>1573400</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1040,71 +1059,77 @@
       <c r="N10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="3">
         <v>5154800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2565200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>4899700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2375300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>4890400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2469300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>5115300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2491600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>4971000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2546000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>5681500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>2935600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>6930900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>3670100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>7063100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>3530000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>9641800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>3155600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>4328300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>3166600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>9468100</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1140,8 +1165,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1241,8 +1268,14 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,8 +1375,14 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1380,71 +1419,77 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>74200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>334500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>317700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>77300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>4467600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>60300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>482500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>424300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>155600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>43600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>111300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>26200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>440100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>39200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>-408200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>23900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>3320400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>2228500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>166900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>800400</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1481,71 +1526,77 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3">
         <v>2749100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1379000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>2497200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>1204500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>2408900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>1230900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>2442400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>1195500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>2262100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>1177000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>2561500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>1310200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>2838000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>1545900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>2936300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>1512000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>2523100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>1157400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>2330000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>1158400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>2442000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,8 +1629,10 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1616,71 +1669,77 @@
       <c r="N17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="3">
         <v>8885200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4354000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>7790800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3737600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>12769600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3597900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>7601800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3922000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>6965800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3438600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>7327600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3742900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>8979700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>4414900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>8360700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>4531200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>12517400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>6272300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>8561100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>4329400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>9482300</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1717,71 +1776,77 @@
       <c r="N18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="3">
         <v>231500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>45400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>432000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>227400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-4368900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>491100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>521200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>47600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1059200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>607200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1136700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>581500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1503600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1010600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>2219900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>817000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1281100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-1137500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>1772200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>814700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>1559200</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,8 +1882,10 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1855,71 +1922,77 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
         <v>170600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-240300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-29400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-327500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>173500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-290800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>42000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-293100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>44900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-307200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>532400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>152700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-448300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-24700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-462900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>4700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-364400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-59300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-383200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-36200</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1956,71 +2029,77 @@
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>3151100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1184000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2899800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1104400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-1786600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1432300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>3005600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>950100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>3366200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1476900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>4230500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>2044400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>4339300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>2108200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>5131500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1866100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>1246800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-344500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>4042800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>1589900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>3964900</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2057,71 +2136,77 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3">
         <v>767600</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
         <v>683300</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U22" s="3">
         <v>648300</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3">
         <v>632100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="3">
         <v>597400</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3">
         <v>699300</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC22" s="3">
         <v>792700</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE22" s="3">
         <v>863500</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG22" s="3">
         <v>747600</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI22" s="3">
         <v>720300</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK22" s="3">
         <v>791700</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2158,71 +2243,77 @@
       <c r="N23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-365500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-194900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-280700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-100100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-4843800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>200300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-68900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-245500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>506700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>300000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>969800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>734200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>708600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>562300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>1331700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>354100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-2023900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-1501900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>992600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>431500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>731300</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2259,71 +2350,77 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="3">
         <v>2175300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>2223000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>111000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>54400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>4213900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-38800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-7500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-40200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-6105100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-240800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>181100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>89500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>141300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>129800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>461100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>130400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>82800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-56500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>326100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>171300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>36200</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,8 +2520,14 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2461,71 +2564,77 @@
       <c r="N26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-2540800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2417900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-391700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-154500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-9057700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>239100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-61400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-205300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>6611800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>540700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>788700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>644700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>567400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>432400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>870500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>223700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-2106700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-1445400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>666500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>260200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2562,71 +2671,77 @@
       <c r="N27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-2704800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2486600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-525600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-222000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-9231100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>149700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-160500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-228500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>6529000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>519000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>739600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>610900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>407400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>368700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>648200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>197400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>584100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>220700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,8 +2841,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2764,11 +2885,11 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2788,27 +2909,27 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>18700</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
@@ -2827,8 +2948,14 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +3055,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,8 +3162,14 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3067,71 +3206,77 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-170600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>240300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>29400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>327500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-173500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>290800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-42000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>293100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-44900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>307200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-532400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-152700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>2300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>448300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>24700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>462900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>364400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>59300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>383200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>36200</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3168,71 +3313,77 @@
       <c r="N33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-2704800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2486600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-525600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-222000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-9231100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>149700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-160500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-228500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>6529000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>519000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>739600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>610900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>426100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>368700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>648200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>197400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>584100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>220700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,8 +3483,14 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3370,177 +3527,189 @@
       <c r="N35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-2704800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2486600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-525600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-222000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-9231100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>149700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-160500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-228500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>6529000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>519000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>739600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>610900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>426100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>368700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>648200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>197400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>584100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>220700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3745,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,917 +3784,973 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2368300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2404600</v>
+      </c>
+      <c r="F41" s="3">
         <v>2073200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1693500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2407000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3027200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2413600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>595700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1386300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3218700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3483300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2603700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2890000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3937500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>3897600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2601600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3560300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>7484600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>4784700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>5351100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>4623500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>4816400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2966300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>3930500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>3561800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>3663300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2630100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1999900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2515600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2267600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2816600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>2308000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>1844600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>3925400</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1635000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1724800</v>
+      </c>
+      <c r="F42" s="3">
         <v>1693100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1814400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1684000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1704100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>2094600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>2237200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1929000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>2272600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1928500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>2036000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1824200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1772200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>2112200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>2048900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>2308900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>2592100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>1643300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>1573400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>3134900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1250700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>1293200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1098500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>1074500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>1166200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>1527600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>1307000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>1882800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>1651300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>1694600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>1564700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>1831500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>1570100</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6810800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5228400</v>
+      </c>
+      <c r="F43" s="3">
         <v>5790200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4151500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5379400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3363700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5261000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3594800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>6108500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4708700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>5289000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3777300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>5167300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3950800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>5447200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3698500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>4971500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3694600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>4720100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>3787500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>4649900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>3621600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>4836600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>4119300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>5433800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>4973200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>6253600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>4826800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>6313500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>4907900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>5703000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>4508400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>5900700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>4597300</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>314800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>275900</v>
+      </c>
+      <c r="F44" s="3">
         <v>285100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>267800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>241000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>307500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>350200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>331100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>418600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>381300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>385300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>411600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>394400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>356600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>381000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>352500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>336200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>305700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>385500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>366100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>350200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>286300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>282300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>279300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>307600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>303500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>366300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>371700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>388800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>460100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>344500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>352500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>357900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>318400</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1347900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2692300</v>
+      </c>
+      <c r="F45" s="3">
         <v>1363400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>2894900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1264600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1107800</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>25672300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>1444700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1611400</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1315800</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S45" s="3">
         <v>1360100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U45" s="3">
         <v>1176200</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W45" s="3">
         <v>1005800</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y45" s="3">
         <v>853800</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="3">
         <v>1030900</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3">
         <v>938600</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE45" s="3">
         <v>1203500</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG45" s="3">
         <v>1038600</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI45" s="3">
         <v>1109000</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK45" s="3">
         <v>932200</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12476700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>12325900</v>
+      </c>
+      <c r="F46" s="3">
         <v>11205000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10822100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>10976000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>9510300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>10119300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>32431200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>9842500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>12026100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>11087000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>10440000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>10276000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>11333000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>11838000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>10061700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>11177000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>15253300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>11533600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>12083900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>12758400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>10762900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>9378500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>10458600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>10377800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>11044900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>10777500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>9708800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>11100700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>10325500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>10558800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>9842500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>9934700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>11343400</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>439300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>879400</v>
+      </c>
+      <c r="F47" s="3">
         <v>504500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>963000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>443100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1087100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>1502300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1340400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1891300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1923300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1857500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1994500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2495700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1585000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>5714100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1270900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>8292400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>4296300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>7922800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>3883300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>7397500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>3628500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>7896300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>4272000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>9769100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>3208000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>6742300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>3669200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>5077900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>2973800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>3953000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>2599000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>4036200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>3033800</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8729400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8634500</v>
+      </c>
+      <c r="F48" s="3">
         <v>8719900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>8716400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>8186300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>8310400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>8917000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>8012400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>21752100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>22335600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>20854100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>21637600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>21337500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>21695700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>21641400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>21245200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>20531400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>19685100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>19160200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>19327100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>18865200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>18085900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>18349000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>19645100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>20250600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>22770300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>24117600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>23400900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>23709900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>19099100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>17481300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>17492200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>17704200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>18168600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19090300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>19337800</v>
+      </c>
+      <c r="F49" s="3">
         <v>19489600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>19627700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>18334400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>17642600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>19252700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>18791400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>28183200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>29061600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>27973100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>29126600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>28971100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>29647100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>29826600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>29278600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>28359200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>27877600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>31416400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>31655500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>30996200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>29510100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>30568200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>32440400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>32756800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>35897900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>42218100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>40927000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>41849100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>42179800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>37227500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>39297400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>39766300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>40246100</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4850,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,109 +4957,121 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1820600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>564800</v>
+      </c>
+      <c r="F52" s="3">
         <v>2473300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>618900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>2471900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>576700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1777800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2852200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2368100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>475300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2436500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>792600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2602100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>4440400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>877200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>10577400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3775700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>7893300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>8560300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>12529700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>7984700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>11035200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1120900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>5791600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1022200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>8919000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>1248300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>3597400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>1498800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>3106300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1190700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>2232200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>991500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>2731800</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,109 +5171,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>43200700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>43130200</v>
+      </c>
+      <c r="F54" s="3">
         <v>43051700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>42803300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>41021400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>38992600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>42229500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>65424800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>64912100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>68706800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>65164100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>66953100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>66580800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>68701100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>69897300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>72433700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>72135600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>75005600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>78593200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>79479500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>78002100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>73022600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>67313000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>72607700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>74176400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>81840100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>85103700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>81303400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>83236400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>77620700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>70411200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>71463300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>72432900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>75523700</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5321,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,614 +5360,652 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8401900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5263600</v>
+      </c>
+      <c r="F57" s="3">
         <v>7394100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4184400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>7442700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4504600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>7694600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3896900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>9767000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6014100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>8355200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5253300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>8712500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5864700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>8407800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>4971500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>10505600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5595000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>8740100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>4093300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>7438800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>4122300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>6131900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>3279300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>7170600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>5046700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>7912200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>4031500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>8182000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>5287600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>6761900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>3978100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>7476300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>5100200</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3664200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4158700</v>
+      </c>
+      <c r="F58" s="3">
         <v>4719000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>5234300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>4856200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4548100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4255000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>14453000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>5916500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>7305200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>7348600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>9137600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>6526500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>6235800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>6218100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>4662500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>4146700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>7044500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>5442700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>5541700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>6075000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>4233000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>4583400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>4700700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>4584000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>4388300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>5239300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>4011500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>6679600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>6594700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>7155100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>6297000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>5512000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>5139700</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>684900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2679300</v>
+      </c>
+      <c r="F59" s="3">
         <v>1261300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3204900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1134900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1666800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>23400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>11864400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>24800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2823000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>26500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1748900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>46700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3563100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>10000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>5817000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>297100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>5100700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>261700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>3603300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>269800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2761800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>58100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>3511600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>46900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>3550100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>51400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>3972700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>77800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>3354700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>47600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>3631100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>81300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>3362100</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12751100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>13523500</v>
+      </c>
+      <c r="F60" s="3">
         <v>13374400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>14391100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>13433900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>11917400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>11973000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>32086100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>15708300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>17707500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>15730300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>18059000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>15285700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>15663700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>14635800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>15451000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>14949400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>17740200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>14444500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>13238300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>13783600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>11117000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>10773400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>11491600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>11801500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>12985100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>13202900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>12015700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>14939300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>15236900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>13964600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>13906200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>13069500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>13602000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13211100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>12289500</v>
+      </c>
+      <c r="F61" s="3">
         <v>12463900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>11389300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>11569400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>11542600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>13305800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>14091900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>27997600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>28768700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>27484100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>25672500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>28097600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>28862900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>30465600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>28256900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>28920600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>28346000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>27642900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>26142800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>26892200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>25944400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>28929400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>29868000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>32482900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>33295700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>37070600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>33809700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>35096500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>27956700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>27723200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>25709700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>28833500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>28755500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1236000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>861800</v>
+      </c>
+      <c r="F62" s="3">
         <v>1307100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>811500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1341300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>909000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1361800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1010400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2198700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1434700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2012100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1303500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2221900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3434700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3584200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4216400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3527600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>5027000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>3509600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>7147400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>5774600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>7196200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>5323400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>7909100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>5880000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>9145500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>7214000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>9204200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>7100600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>8702600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>4465800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>6158700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>4571000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>7052500</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +6105,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6212,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,109 +6319,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27666300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>27332400</v>
+      </c>
+      <c r="F66" s="3">
         <v>27443400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>27302400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>26621300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>25160000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>26950700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>47760600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>46563800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>49349000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>46322000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>47014200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>46840500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>52019500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>52772700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>53294000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>52782600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>56127100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>50548600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>51473700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>51146900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>46875800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>46319400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>50701100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>51678600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>58165000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>60332000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>57835400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>59776500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>54521000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>48500700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>48032000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>48898300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>51854100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6469,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6572,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6679,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6451,8 +6786,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,8 +6893,14 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6566,8 +6913,8 @@
       <c r="F72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="3">
-        <v>-631500</v>
+      <c r="G72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>8</v>
@@ -6578,83 +6925,89 @@
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3">
         <v>-1592800</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72" s="3">
         <v>3835600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>4038300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>6418700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>6722300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>6912200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>16264400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>16093200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>15713400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>15440700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>9793600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>9747300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>9963300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>9994200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>10410000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>9644100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>9345900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>9238400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>9251800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>10729700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>10540800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>10403600</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +7107,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7214,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,109 +7321,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13972100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>14346600</v>
+      </c>
+      <c r="F76" s="3">
         <v>14009200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>13927200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>12943100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>12379100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>13659400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>13652600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>14237800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>15083500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>14809500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>15751100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>15713800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>16681600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>17124600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>19139700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>19352900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>18878500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>28044600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>28005900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>26855200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>26146800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>20993600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>21906600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>22497800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>23675100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>24771700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>23468000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>23459900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>23099700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>21910500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>23431300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>23534500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>23669600</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,114 +7535,126 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7302,71 +7691,77 @@
       <c r="N81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-2704800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2486600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-525600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-222000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-9231100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>149700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-160500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-228500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>6529000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>519000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>739600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>610900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>426100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>368700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>648200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>197400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-2324400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-1575000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>584100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>220700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>576500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,109 +7797,117 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>794400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>766100</v>
+      </c>
+      <c r="F83" s="3">
         <v>839800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>426400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1264400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>903100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>873200</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
         <v>1304900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1322000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1220800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>474600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1229700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>2749100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1379000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>2497200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1204500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>2408900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1232000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>2442400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1195500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>2262100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1177000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>2561500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>1310200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>2838000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>1545900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>2936300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>1512000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>2523100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>1157400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>2330000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>1158400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>2442000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +8007,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +8114,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8221,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8328,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,109 +8435,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>161400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1365500</v>
+      </c>
+      <c r="F89" s="3">
         <v>616000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>709300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>322100</v>
       </c>
-      <c r="G89" s="3">
-        <v>1590200</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>1681300</v>
+      </c>
+      <c r="J89" s="3">
         <v>306700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>243200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>477900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1626000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P89" s="3">
         <v>924600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2660500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1120900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2712600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1169700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>2613800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1117800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2073000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1334100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>2514400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1574500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>4396400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>2585500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>3281600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1699100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>3692700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>1776400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>2382400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>1032300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>2830600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>1021100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>2482600</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,109 +8585,117 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-506200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-237200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-449400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-468600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-591200</v>
       </c>
-      <c r="G91" s="3">
-        <v>-392400</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>-368600</v>
+      </c>
+      <c r="J91" s="3">
         <v>-403700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-109300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1136000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-613500</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1145200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1003000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2713000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1438000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-1151000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-2364000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-872000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-1187000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-924700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-1275700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-2787800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-90500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-1239300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-1778000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-937100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-2501000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-61000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-2622500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-674200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-536900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-3041500</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8795,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,109 +8902,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-473900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-151500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-492800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-374600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-605300</v>
       </c>
-      <c r="G94" s="3">
-        <v>-251600</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>-316800</v>
+      </c>
+      <c r="J94" s="3">
         <v>6718700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-148900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-695900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1091000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
         <v>-1254900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-2559700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1699100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-3290400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-822600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-3139600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1165200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-2391800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-889800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1457200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-994300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-1762900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1220700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1480300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-1075500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-2337500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-1498800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-2488800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-1073300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-2426600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-1653600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-2909700</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,109 +9052,117 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>164400</v>
+      </c>
+      <c r="F96" s="3">
         <v>56300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>58700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>37800</v>
       </c>
-      <c r="G96" s="3">
-        <v>42400</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
+        <v>31100</v>
+      </c>
+      <c r="J96" s="3">
         <v>48000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>50400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>42100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>27600</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3">
         <v>41300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-34300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-17700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-40300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-28300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-34700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-19400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-361800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-25400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-33900</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-388400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-43600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-38500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-7300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-289400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-29900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-40200</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-18800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-243800</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-18700</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9262,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9369,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,307 +9476,331 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>249000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-858300</v>
+      </c>
+      <c r="F100" s="3">
         <v>271000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1239000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-452900</v>
       </c>
-      <c r="G100" s="3">
-        <v>-398600</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>-423400</v>
+      </c>
+      <c r="J100" s="3">
         <v>-5378100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-789700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1533100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-939500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>-647500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>1220600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1824200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-4320800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-4462300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>2662500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-483500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>762400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-576600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-144600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1498700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-2033500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-1206500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-29200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-128600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1281100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>279900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-432900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>548300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-1607500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-1103500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-429300</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="F101" s="3">
         <v>-23400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-42900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-4300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-11100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-5300</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3">
         <v>4300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-34200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>10800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-170400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>160000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-23300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>12200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-20700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>156700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-37900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-37700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>51700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-14800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-9000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-163600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-90500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-17500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>5900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>7200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-14200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-16600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-56000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-20900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-65900</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>332300</v>
+      </c>
+      <c r="F102" s="3">
         <v>409500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-925400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-717700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>902800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1623900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-738200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1755300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-415600</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-973500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1298100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1258200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-4919300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-3958500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>2098800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-568600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>495400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-147100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>903600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-927900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>436400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>67600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>1754600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>491200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>80000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>564600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-553600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>490700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-1259400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-1756800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-922300</v>
       </c>
     </row>
